--- a/output/yearly_surface_area_iteration_87_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_87_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497626177109</v>
+        <v>10.84497604978966</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907169644911</v>
+        <v>37.78907095780465</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.526257827205296</v>
+        <v>8.772897485149498</v>
       </c>
       <c r="C2" t="n">
-        <v>6.053456344385832</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="D2" t="n">
-        <v>19.14702547592554</v>
+        <v>24.54761959698725</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.61469723604552</v>
+        <v>23.37541283811656</v>
       </c>
       <c r="C3" t="n">
-        <v>19.02136176978195</v>
+        <v>14.54950097693773</v>
       </c>
       <c r="D3" t="n">
-        <v>62.91530162665685</v>
+        <v>84.184865639164</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.69358120975053</v>
+        <v>46.67326760759762</v>
       </c>
       <c r="C4" t="n">
-        <v>50.37445645260809</v>
+        <v>42.65301075870693</v>
       </c>
       <c r="D4" t="n">
-        <v>85.75271672284615</v>
+        <v>115.1963121209122</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.16039439535329</v>
+        <v>60.54928965942204</v>
       </c>
       <c r="C5" t="n">
-        <v>76.03635969391547</v>
+        <v>78.2452920284708</v>
       </c>
       <c r="D5" t="n">
-        <v>64.35356201337844</v>
+        <v>78.78525326580655</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.72588107299945</v>
+        <v>57.47936458824226</v>
       </c>
       <c r="C6" t="n">
-        <v>98.85806682683683</v>
+        <v>89.31842438467058</v>
       </c>
       <c r="D6" t="n">
-        <v>47.01393406097126</v>
+        <v>50.27431818677493</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.99752208743954</v>
+        <v>41.32176087174825</v>
       </c>
       <c r="C7" t="n">
-        <v>101.0287110009265</v>
+        <v>68.21084874336412</v>
       </c>
       <c r="D7" t="n">
-        <v>38.98618308334508</v>
+        <v>39.82459562277186</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.27385085622263</v>
+        <v>21.02903582496668</v>
       </c>
       <c r="C8" t="n">
-        <v>70.26368319294421</v>
+        <v>40.55599766243574</v>
       </c>
       <c r="D8" t="n">
-        <v>36.55046702910875</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.098436812331936</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>40.93593402397924</v>
+        <v>29.28749751309084</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.700710430505953</v>
+        <v>7.694466109130624</v>
       </c>
       <c r="C21" t="n">
-        <v>95.29629157751118</v>
+        <v>94.25720983685014</v>
       </c>
       <c r="D21" t="n">
-        <v>8.663299234319197</v>
+        <v>8.656274372771952</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.908558594784804</v>
+        <v>9.913688317484292</v>
       </c>
       <c r="C2" t="n">
-        <v>9.356055621472102</v>
+        <v>5.289656630481814</v>
       </c>
       <c r="D2" t="n">
-        <v>30.41945261608742</v>
+        <v>23.06223532046182</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.08731879241574</v>
+        <v>26.4384656753666</v>
       </c>
       <c r="C3" t="n">
-        <v>21.35301256736813</v>
+        <v>15.18272824617692</v>
       </c>
       <c r="D3" t="n">
-        <v>63.30800070835556</v>
+        <v>83.76762286485911</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.51115606320987</v>
+        <v>45.71606359595697</v>
       </c>
       <c r="C4" t="n">
-        <v>48.85569275413827</v>
+        <v>38.99011007416208</v>
       </c>
       <c r="D4" t="n">
-        <v>96.58826613461819</v>
+        <v>127.4995743505333</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.7865695042135</v>
+        <v>64.91806694332035</v>
       </c>
       <c r="C5" t="n">
-        <v>83.71853547964676</v>
+        <v>78.417097876714</v>
       </c>
       <c r="D5" t="n">
-        <v>78.17166095065228</v>
+        <v>99.67193567365744</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.81646390369741</v>
+        <v>69.07184147998861</v>
       </c>
       <c r="C6" t="n">
-        <v>109.9675238480937</v>
+        <v>105.4995900460665</v>
       </c>
       <c r="D6" t="n">
-        <v>55.90955000915161</v>
+        <v>61.22276858453534</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.41779222031519</v>
+        <v>54.85613472249477</v>
       </c>
       <c r="C7" t="n">
-        <v>121.1506119471691</v>
+        <v>97.91460728305563</v>
       </c>
       <c r="D7" t="n">
-        <v>43.41779222031519</v>
+        <v>44.85507085933252</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.28629478120835</v>
+        <v>32.04424506661589</v>
       </c>
       <c r="C8" t="n">
-        <v>101.9741340401162</v>
+        <v>64.17193868809275</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.42499894494763</v>
+        <v>14.8656237377052</v>
       </c>
       <c r="C9" t="n">
-        <v>63.12343213995715</v>
+        <v>39.82655911818034</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>39.85895679242051</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
         <v>34.71459882216721</v>
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>28.61794557879453</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.889528266080364</v>
+        <v>7.880074168372414</v>
       </c>
       <c r="C21" t="n">
-        <v>104.5362495255648</v>
+        <v>103.4259734598879</v>
       </c>
       <c r="D21" t="n">
-        <v>9.861910332600456</v>
+        <v>9.850092710465518</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.68337851761379</v>
+        <v>12.66356363707961</v>
       </c>
       <c r="C2" t="n">
-        <v>9.13221714490383</v>
+        <v>6.542366701100745</v>
       </c>
       <c r="D2" t="n">
-        <v>30.13769102496859</v>
+        <v>31.96668699798039</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.78712497909446</v>
+        <v>29.20208546282137</v>
       </c>
       <c r="C3" t="n">
-        <v>28.62285431731576</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D3" t="n">
-        <v>70.51893759604839</v>
+        <v>82.30972752405259</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.77917318646925</v>
+        <v>46.97957289132261</v>
       </c>
       <c r="C4" t="n">
-        <v>50.89772797897164</v>
+        <v>38.02014334236623</v>
       </c>
       <c r="D4" t="n">
-        <v>103.1610670145506</v>
+        <v>136.2675630971615</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.41841411512095</v>
+        <v>66.24342634405355</v>
       </c>
       <c r="C5" t="n">
-        <v>85.68203088814039</v>
+        <v>75.25096153051803</v>
       </c>
       <c r="D5" t="n">
-        <v>92.30882789180636</v>
+        <v>118.9878217547134</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.6064109527176</v>
+        <v>77.24292762243481</v>
       </c>
       <c r="C6" t="n">
-        <v>120.7147159664836</v>
+        <v>113.2279079738974</v>
       </c>
       <c r="D6" t="n">
-        <v>65.00642423670256</v>
+        <v>74.50581502299471</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>52.70021676396878</v>
+        <v>67.61198264377359</v>
       </c>
       <c r="C7" t="n">
-        <v>137.7990895157865</v>
+        <v>121.7494780467597</v>
       </c>
       <c r="D7" t="n">
-        <v>48.80758711663017</v>
+        <v>51.14316490503334</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>35.79943003535994</v>
+        <v>43.81049130201391</v>
       </c>
       <c r="C8" t="n">
-        <v>128.4273259310465</v>
+        <v>93.87962421860124</v>
       </c>
       <c r="D8" t="n">
-        <v>40.63944621729671</v>
+        <v>40.72289477215769</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.41562343626167</v>
+        <v>22.2984356065578</v>
       </c>
       <c r="C9" t="n">
-        <v>92.1890546718882</v>
+        <v>57.243745139223</v>
       </c>
       <c r="D9" t="n">
-        <v>37.16405934426299</v>
+        <v>37.60780930658255</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>10.2494460323367</v>
       </c>
       <c r="C10" t="n">
-        <v>55.09077242380977</v>
+        <v>39.43189654107314</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.686282702997524</v>
       </c>
       <c r="C11" t="n">
-        <v>39.09319358310798</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
-        <v>37.6716229073586</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>33.82120841130262</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.063568675687664</v>
+        <v>8.051925922115979</v>
       </c>
       <c r="C21" t="n">
-        <v>112.8899614596273</v>
+        <v>111.7204721693592</v>
       </c>
       <c r="D21" t="n">
-        <v>11.08740692907054</v>
+        <v>11.07139814290947</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.365873098514571</v>
+        <v>11.34016773175491</v>
       </c>
       <c r="C2" t="n">
-        <v>6.063273821428301</v>
+        <v>4.343251843587889</v>
       </c>
       <c r="D2" t="n">
-        <v>24.41017491839269</v>
+        <v>25.94955531865169</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.2232419439583</v>
+        <v>34.30226478638355</v>
       </c>
       <c r="C3" t="n">
-        <v>41.20395114723863</v>
+        <v>27.16005023798801</v>
       </c>
       <c r="D3" t="n">
-        <v>77.99985510240909</v>
+        <v>92.73097940463248</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.78145547704723</v>
+        <v>31.81746134693488</v>
       </c>
       <c r="C4" t="n">
-        <v>72.0838434366178</v>
+        <v>59.09139431861551</v>
       </c>
       <c r="D4" t="n">
-        <v>101.042455468786</v>
+        <v>132.4259843304438</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.011266555299</v>
+        <v>43.51596699073988</v>
       </c>
       <c r="C5" t="n">
-        <v>72.1339125695344</v>
+        <v>67.64241682260524</v>
       </c>
       <c r="D5" t="n">
-        <v>64.52536786162162</v>
+        <v>77.63169971331654</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.72459622565894</v>
+        <v>41.98247707670636</v>
       </c>
       <c r="C6" t="n">
-        <v>90.72723234026475</v>
+        <v>80.18129850124551</v>
       </c>
       <c r="D6" t="n">
-        <v>32.12082138754715</v>
+        <v>33.65038431076368</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.71509754378595</v>
+        <v>29.04500583014188</v>
       </c>
       <c r="C7" t="n">
-        <v>90.30900781825558</v>
+        <v>65.99504417487908</v>
       </c>
       <c r="D7" t="n">
-        <v>28.56591295046944</v>
+        <v>28.62579956042849</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.76762889372977</v>
+        <v>15.43798264928109</v>
       </c>
       <c r="C8" t="n">
-        <v>67.92712365683681</v>
+        <v>42.14152020479433</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>27.70492021384499</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>42.04530892977813</v>
+        <v>30.06405994715006</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="11">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.55471281509523</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
         <v>25.49598787928967</v>
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>24.27567548291088</v>
       </c>
     </row>
     <row r="15">
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>74.64718669240621</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.486987919035423</v>
+        <v>6.704355072301468</v>
       </c>
       <c r="C2" t="n">
-        <v>2.686061718819273</v>
+        <v>2.215804568485051</v>
       </c>
       <c r="D2" t="n">
-        <v>17.41816776874691</v>
+        <v>18.06710300125405</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.39705234533899</v>
+        <v>37.75310796681109</v>
       </c>
       <c r="C3" t="n">
-        <v>32.62838495064275</v>
+        <v>22.24149423971149</v>
       </c>
       <c r="D3" t="n">
-        <v>80.47385931711105</v>
+        <v>93.45747270577512</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.87676711981719</v>
+        <v>47.41350537659971</v>
       </c>
       <c r="C4" t="n">
-        <v>89.47943100816704</v>
+        <v>65.65143247839271</v>
       </c>
       <c r="D4" t="n">
-        <v>114.5581761131518</v>
+        <v>146.3628747399315</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.61289797155305</v>
+        <v>47.71293842639499</v>
       </c>
       <c r="C5" t="n">
-        <v>102.8135283272472</v>
+        <v>88.25911861178827</v>
       </c>
       <c r="D5" t="n">
-        <v>81.85321484157782</v>
+        <v>101.2918193856647</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.20511282139213</v>
+        <v>50.47557646614552</v>
       </c>
       <c r="C6" t="n">
-        <v>106.2643715076748</v>
+        <v>96.24170919501908</v>
       </c>
       <c r="D6" t="n">
-        <v>39.72838434775569</v>
+        <v>43.19002675292993</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.39759212468673</v>
+        <v>27.42806736124739</v>
       </c>
       <c r="C7" t="n">
-        <v>110.9100016441706</v>
+        <v>86.89547105058944</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>12.76762889372977</v>
       </c>
       <c r="C8" t="n">
-        <v>87.2871883845839</v>
+        <v>56.74501730546564</v>
       </c>
       <c r="D8" t="n">
-        <v>28.62285431731576</v>
+        <v>28.87319998189869</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>49.36718330805084</v>
+        <v>35.94374694788421</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
         <v>29.49759152179966</v>
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>64.99562501195582</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.565527735375168</v>
+        <v>7.693956758182253</v>
       </c>
       <c r="C2" t="n">
-        <v>4.994150571503524</v>
+        <v>5.53411180883927</v>
       </c>
       <c r="D2" t="n">
-        <v>14.04586440465912</v>
+        <v>29.87654613563893</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.44413517741383</v>
+        <v>30.12983704333461</v>
       </c>
       <c r="C3" t="n">
-        <v>20.52343575727957</v>
+        <v>14.8194815956056</v>
       </c>
       <c r="D3" t="n">
-        <v>75.88909753827845</v>
+        <v>86.57542129900497</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.85270645329653</v>
+        <v>59.79334392715199</v>
       </c>
       <c r="C4" t="n">
-        <v>85.24220791663781</v>
+        <v>60.30385273336033</v>
       </c>
       <c r="D4" t="n">
-        <v>127.422998029602</v>
+        <v>158.6023233687765</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.26423866782519</v>
+        <v>59.61662934038758</v>
       </c>
       <c r="C5" t="n">
-        <v>135.5548142638784</v>
+        <v>105.0224606618026</v>
       </c>
       <c r="D5" t="n">
-        <v>101.9544990860313</v>
+        <v>127.6026578594792</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.87430490278997</v>
+        <v>57.51961624411638</v>
       </c>
       <c r="C6" t="n">
-        <v>133.9172590931947</v>
+        <v>118.9838947638964</v>
       </c>
       <c r="D6" t="n">
-        <v>53.69570893607505</v>
+        <v>61.46427851978007</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.75797564760332</v>
+        <v>41.32176087174825</v>
       </c>
       <c r="C7" t="n">
-        <v>133.1878205489393</v>
+        <v>113.0659196026967</v>
       </c>
       <c r="D7" t="n">
-        <v>34.85400699617026</v>
+        <v>35.75230614555609</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.93867397844697</v>
+        <v>19.27661617288612</v>
       </c>
       <c r="C8" t="n">
-        <v>116.4107340310655</v>
+        <v>84.36648896444964</v>
       </c>
       <c r="D8" t="n">
-        <v>30.29182541453534</v>
+        <v>30.54217107911827</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>75.88124355664445</v>
+        <v>51.69687061022852</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>29.7312474754104</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.989421759431538</v>
       </c>
       <c r="C10" t="n">
-        <v>44.69897297435728</v>
+        <v>36.86953503298896</v>
       </c>
       <c r="D10" t="n">
-        <v>30.89069151412589</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>34.29539255245382</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
         <v>29.852984190737</v>
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>26.4698816019025</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.232895190084747</v>
+        <v>4.485605260703677</v>
       </c>
       <c r="C2" t="n">
-        <v>2.271764187627119</v>
+        <v>2.490693925674158</v>
       </c>
       <c r="D2" t="n">
-        <v>9.701630813366981</v>
+        <v>20.60884780754904</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.87610416728243</v>
+        <v>31.35702167364312</v>
       </c>
       <c r="C3" t="n">
-        <v>21.39719121405923</v>
+        <v>18.84464718301752</v>
       </c>
       <c r="D3" t="n">
-        <v>73.42981953914018</v>
+        <v>91.52833846693014</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.80464187351743</v>
+        <v>66.11089040398021</v>
       </c>
       <c r="C4" t="n">
-        <v>80.62210322045232</v>
+        <v>57.30461349688632</v>
       </c>
       <c r="D4" t="n">
-        <v>136.3696648584032</v>
+        <v>167.7659564402162</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.35674393620265</v>
+        <v>62.66004722355269</v>
       </c>
       <c r="C5" t="n">
-        <v>159.8776136365931</v>
+        <v>121.5894531709675</v>
       </c>
       <c r="D5" t="n">
-        <v>110.4711604203724</v>
+        <v>137.8619213688584</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.96360288614742</v>
+        <v>50.07305990740432</v>
       </c>
       <c r="C6" t="n">
-        <v>170.6670209062655</v>
+        <v>148.6493651431223</v>
       </c>
       <c r="D6" t="n">
-        <v>52.85042416271855</v>
+        <v>59.8542122848153</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.54004335279375</v>
+        <v>12.75584792127881</v>
       </c>
       <c r="C7" t="n">
-        <v>146.1832149100543</v>
+        <v>117.2579822998305</v>
       </c>
       <c r="D7" t="n">
-        <v>35.09355343600648</v>
+        <v>35.81219275551515</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>93.54582999915733</v>
+        <v>65.34021845614646</v>
       </c>
       <c r="D8" t="n">
         <v>32.12769362147687</v>
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>28.06718511671205</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
         <v>23.34596040698915</v>
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>21.14586380177204</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.684900044665779</v>
+        <v>5.500732386894879</v>
       </c>
       <c r="C2" t="n">
-        <v>6.935065782799468</v>
+        <v>2.114684554947629</v>
       </c>
       <c r="D2" t="n">
-        <v>8.993790718605029</v>
+        <v>19.41602434688917</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5585576904542</v>
+        <v>23.47358760854124</v>
       </c>
       <c r="C3" t="n">
-        <v>14.58386214658637</v>
+        <v>14.04390090925062</v>
       </c>
       <c r="D3" t="n">
-        <v>65.49238935030472</v>
+        <v>87.76333602114362</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.46455625722054</v>
+        <v>63.95399069774997</v>
       </c>
       <c r="C4" t="n">
-        <v>67.23400977763856</v>
+        <v>52.03361007278519</v>
       </c>
       <c r="D4" t="n">
-        <v>141.1173967561408</v>
+        <v>174.12179107751</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.46307578789757</v>
+        <v>78.85888434362505</v>
       </c>
       <c r="C5" t="n">
-        <v>155.8033606639688</v>
+        <v>114.8644813968768</v>
       </c>
       <c r="D5" t="n">
-        <v>130.4251825091888</v>
+        <v>162.0374585859361</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.22148373719484</v>
+        <v>64.16113946334606</v>
       </c>
       <c r="C6" t="n">
-        <v>211.1199350597554</v>
+        <v>171.0695374650067</v>
       </c>
       <c r="D6" t="n">
-        <v>70.60140440320514</v>
+        <v>83.56243759467154</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.99645822427728</v>
+        <v>28.98511922018283</v>
       </c>
       <c r="C7" t="n">
-        <v>194.3320493171349</v>
+        <v>163.2508987483851</v>
       </c>
       <c r="D7" t="n">
-        <v>41.02232782195297</v>
+        <v>42.22006002113408</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.926230053461247</v>
+        <v>8.094509821514951</v>
       </c>
       <c r="C8" t="n">
-        <v>137.4397698560322</v>
+        <v>104.0603479116407</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>66.00780689503428</v>
+        <v>49.03437083631118</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3069,10 +3069,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
         <v>24.91184799526281</v>
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>25.05518316008284</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
         <v>21.69662426385451</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.1456838753228</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.186753047985146</v>
+        <v>4.223478623669778</v>
       </c>
       <c r="C2" t="n">
-        <v>3.773838175124739</v>
+        <v>1.461822331623501</v>
       </c>
       <c r="D2" t="n">
-        <v>6.323436963053706</v>
+        <v>14.9431818063407</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.10204500797944</v>
+        <v>21.73589417202438</v>
       </c>
       <c r="C3" t="n">
-        <v>20.73451151369264</v>
+        <v>11.388273369263</v>
       </c>
       <c r="D3" t="n">
-        <v>59.82279635827939</v>
+        <v>84.88190650917923</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.17628228507048</v>
+        <v>58.04485126588842</v>
       </c>
       <c r="C4" t="n">
-        <v>55.09666291003525</v>
+        <v>45.74158903626739</v>
       </c>
       <c r="D4" t="n">
-        <v>142.1001262080918</v>
+        <v>177.7591663217445</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.57445524683396</v>
+        <v>87.0810213666921</v>
       </c>
       <c r="C5" t="n">
-        <v>148.3666218042992</v>
+        <v>111.1829275059513</v>
       </c>
       <c r="D5" t="n">
-        <v>143.9487571351886</v>
+        <v>178.5553637098887</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.80137783523521</v>
+        <v>77.08192099893833</v>
       </c>
       <c r="C6" t="n">
-        <v>234.4256438108704</v>
+        <v>183.8695640329767</v>
       </c>
       <c r="D6" t="n">
-        <v>85.53476873250337</v>
+        <v>102.4807158555076</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.39759212468673</v>
+        <v>28.26647990067416</v>
       </c>
       <c r="C7" t="n">
-        <v>239.2470067864264</v>
+        <v>198.5241120142688</v>
       </c>
       <c r="D7" t="n">
-        <v>46.05280305851362</v>
+        <v>48.32849423695774</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>174.4074796594459</v>
+        <v>136.0211444233956</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>80.20780568926014</v>
+        <v>60.57186985661969</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>34.02246669067321</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
         <v>25.62361508084176</v>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.87748682561417</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
         <v>24.34439782220815</v>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
         <v>20.17786056538469</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.710826395603696</v>
+        <v>6.244897146713961</v>
       </c>
       <c r="C2" t="n">
-        <v>10.90427175106932</v>
+        <v>10.73933813675586</v>
       </c>
       <c r="D2" t="n">
-        <v>9.450303401079797</v>
+        <v>14.76548547187203</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.00463100108075</v>
+        <v>18.06906649666254</v>
       </c>
       <c r="C3" t="n">
-        <v>17.84326452468578</v>
+        <v>8.541205026947251</v>
       </c>
       <c r="D3" t="n">
-        <v>52.28788272818512</v>
+        <v>78.00967257945155</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.30092318578082</v>
+        <v>49.940523967331</v>
       </c>
       <c r="C4" t="n">
-        <v>52.88871232318417</v>
+        <v>37.50963453615788</v>
       </c>
       <c r="D4" t="n">
-        <v>139.8411247406199</v>
+        <v>178.9460992961789</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.72171740247099</v>
+        <v>88.13640014875742</v>
       </c>
       <c r="C5" t="n">
-        <v>128.3635123302705</v>
+        <v>98.83745012504767</v>
       </c>
       <c r="D5" t="n">
-        <v>158.1840988467673</v>
+        <v>196.61952146803</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>69.6756163181004</v>
+        <v>93.38384162795661</v>
       </c>
       <c r="C6" t="n">
-        <v>235.9149550782128</v>
+        <v>181.5752196481519</v>
       </c>
       <c r="D6" t="n">
-        <v>104.65430527271</v>
+        <v>126.7122126917273</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.92629647338602</v>
+        <v>50.84373185523806</v>
       </c>
       <c r="C7" t="n">
-        <v>282.0659329071511</v>
+        <v>230.5035617324044</v>
       </c>
       <c r="D7" t="n">
-        <v>55.87420709179872</v>
+        <v>61.08434215823654</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.76624623539802</v>
+        <v>14.35315143608837</v>
       </c>
       <c r="C8" t="n">
-        <v>235.2414761530995</v>
+        <v>188.2599397663683</v>
       </c>
       <c r="D8" t="n">
-        <v>38.88702656521616</v>
+        <v>39.38771789438203</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.995312245657018</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>132.9031137147077</v>
+        <v>103.5046787110369</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -3694,7 +3694,7 @@
         <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>55.94489292650449</v>
+        <v>46.83427423109409</v>
       </c>
       <c r="D10" t="n">
         <v>26.90479583488384</v>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
         <v>24.87748682561417</v>
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
         <v>20.61179305066178</v>
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.42652047199962</v>
+        <v>9.252972112526189</v>
       </c>
       <c r="C2" t="n">
-        <v>6.46677212787374</v>
+        <v>2.974695543867836</v>
       </c>
       <c r="D2" t="n">
-        <v>9.648616437337651</v>
+        <v>12.19428823444963</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.992767913171777</v>
+        <v>4.37663126553228</v>
       </c>
       <c r="C2" t="n">
-        <v>6.019095174737195</v>
+        <v>5.927792638242241</v>
       </c>
       <c r="D2" t="n">
-        <v>6.954700736884405</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.41896959000191</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="C3" t="n">
-        <v>28.42159603794516</v>
+        <v>20.44980467946106</v>
       </c>
       <c r="D3" t="n">
-        <v>56.31795705411828</v>
+        <v>84.16523068507905</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.42550733322892</v>
+        <v>67.88490850555419</v>
       </c>
       <c r="C4" t="n">
-        <v>75.78503228162829</v>
+        <v>53.57789921156542</v>
       </c>
       <c r="D4" t="n">
-        <v>145.1376536050315</v>
+        <v>185.0339168102133</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.23969497521902</v>
+        <v>56.67138622764714</v>
       </c>
       <c r="C5" t="n">
-        <v>196.2022786937251</v>
+        <v>149.9619618237003</v>
       </c>
       <c r="D5" t="n">
-        <v>146.0349710067131</v>
+        <v>180.5434028109885</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.15099352447154</v>
+        <v>31.55729820530948</v>
       </c>
       <c r="C6" t="n">
-        <v>236.639484883947</v>
+        <v>192.7249283252829</v>
       </c>
       <c r="D6" t="n">
-        <v>83.9247024975386</v>
+        <v>97.93227874173209</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.785259294677205</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>165.4068167069111</v>
+        <v>132.3494080095125</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>97.9686034067892</v>
+        <v>76.2719791429347</v>
       </c>
       <c r="D8" t="n">
-        <v>25.20146356801562</v>
+        <v>25.03456645829366</v>
       </c>
     </row>
     <row r="9">
@@ -4302,7 +4302,7 @@
         <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>42.71093387325747</v>
+        <v>35.72187196672443</v>
       </c>
       <c r="D9" t="n">
         <v>20.52343575727956</v>
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>23.48831382410494</v>
+        <v>22.34948648717864</v>
       </c>
       <c r="D10" t="n">
         <v>19.50241814486289</v>
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.23654444346124</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="D11" t="n">
         <v>16.52575910558656</v>
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.500552460445631</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C2" t="n">
-        <v>5.411393345808419</v>
+        <v>2.347358760854124</v>
       </c>
       <c r="D2" t="n">
-        <v>19.15291596215102</v>
+        <v>16.94889236611693</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.6512018275519</v>
+        <v>19.63986282345744</v>
       </c>
       <c r="C3" t="n">
-        <v>16.29210315197582</v>
+        <v>7.495643721924397</v>
       </c>
       <c r="D3" t="n">
-        <v>11.24101121362598</v>
+        <v>13.38122120888403</v>
       </c>
     </row>
     <row r="4">
@@ -4554,7 +4554,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
         <v>9.35114688295087</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39813207808077</v>
+        <v>13.39780937749015</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14316205583459</v>
+        <v>70.1414726233308</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576250832715384</v>
+        <v>1.576212867940018</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.041274461307371</v>
+        <v>6.227225688037517</v>
       </c>
       <c r="C2" t="n">
-        <v>6.232134426558751</v>
+        <v>5.592034923389832</v>
       </c>
       <c r="D2" t="n">
-        <v>16.20276411088936</v>
+        <v>21.19691468239288</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.99958339383927</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="C3" t="n">
-        <v>19.30115986549229</v>
+        <v>8.531387549904784</v>
       </c>
       <c r="D3" t="n">
-        <v>24.61241494546753</v>
+        <v>24.38170423496954</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.851298432769</v>
+        <v>22.61554011502952</v>
       </c>
       <c r="C4" t="n">
-        <v>25.38505038870978</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D4" t="n">
-        <v>20.95638649485241</v>
+        <v>22.07950586851077</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.092505268377454</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.424156065963628</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4885,7 +4885,7 @@
         <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44042251808377</v>
+        <v>15.44108937286551</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1413045745726</v>
+        <v>86.14502492230231</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250615266965004</v>
+        <v>3.25075565744537</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.361324212891832</v>
+        <v>7.51331518060084</v>
       </c>
       <c r="C2" t="n">
-        <v>4.014366362665207</v>
+        <v>7.086254929253477</v>
       </c>
       <c r="D2" t="n">
-        <v>17.94634803363169</v>
+        <v>33.37353145816607</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.00172681569702</v>
+        <v>23.01216618754523</v>
       </c>
       <c r="C3" t="n">
-        <v>22.3003991019663</v>
+        <v>16.55226629360122</v>
       </c>
       <c r="D3" t="n">
-        <v>31.86262174133023</v>
+        <v>35.68162031085032</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.94134148411922</v>
+        <v>37.01188845010475</v>
       </c>
       <c r="C4" t="n">
-        <v>38.90077103307561</v>
+        <v>17.51045205294611</v>
       </c>
       <c r="D4" t="n">
-        <v>28.57573042751191</v>
+        <v>29.32873091666921</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.71992416684918</v>
+        <v>19.315886081056</v>
       </c>
       <c r="C5" t="n">
-        <v>29.01064466049325</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="D5" t="n">
-        <v>30.2132855981956</v>
+        <v>30.36054775383262</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.07549676223577</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>36.8302651248191</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.30935800449154</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73402531100304</v>
+        <v>16.736136952021</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0775543971186</v>
+        <v>102.0904354073281</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020207593300913</v>
+        <v>5.020841085606299</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.288674882777567</v>
+        <v>7.123561342014856</v>
       </c>
       <c r="C2" t="n">
-        <v>3.69038962026376</v>
+        <v>4.428663893857362</v>
       </c>
       <c r="D2" t="n">
-        <v>20.775744917271</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.65811511921063</v>
+        <v>24.51424017504286</v>
       </c>
       <c r="C3" t="n">
-        <v>18.40776945462769</v>
+        <v>22.85999529338698</v>
       </c>
       <c r="D3" t="n">
-        <v>38.41087892865646</v>
+        <v>53.10764206123121</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.80844569114741</v>
+        <v>41.30016242225481</v>
       </c>
       <c r="C4" t="n">
-        <v>47.97506506342888</v>
+        <v>30.86025733529424</v>
       </c>
       <c r="D4" t="n">
-        <v>37.59897357724434</v>
+        <v>39.99836496642355</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.15790681613028</v>
+        <v>37.28186906877263</v>
       </c>
       <c r="C5" t="n">
-        <v>52.57258956241671</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="D5" t="n">
-        <v>33.25670348136071</v>
+        <v>33.62485887045326</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.31700669748049</v>
+        <v>16.02015903789946</v>
       </c>
       <c r="C6" t="n">
-        <v>29.98748362621883</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>38.56108632740622</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.34550274309942</v>
+        <v>39.40538935305847</v>
       </c>
     </row>
     <row r="8">
@@ -5535,7 +5535,7 @@
         <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -5549,7 +5549,7 @@
         <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -5574,7 +5574,7 @@
         <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5591,7 +5591,7 @@
         <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06105067422731</v>
+        <v>18.06292647917194</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8268543985306</v>
+        <v>117.8390917926931</v>
       </c>
       <c r="D21" t="n">
-        <v>6.880400256848499</v>
+        <v>6.881114849208356</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.670574739729576</v>
+        <v>8.146542449840032</v>
       </c>
       <c r="C2" t="n">
-        <v>5.748132808365075</v>
+        <v>5.154175447295755</v>
       </c>
       <c r="D2" t="n">
-        <v>28.8859627020539</v>
+        <v>34.88345942729767</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.33137306014569</v>
+        <v>21.75552912610932</v>
       </c>
       <c r="C3" t="n">
-        <v>15.09437095279471</v>
+        <v>18.42740440871263</v>
       </c>
       <c r="D3" t="n">
-        <v>42.95146206079795</v>
+        <v>64.17193868809277</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.38505038870978</v>
+        <v>32.36625831360885</v>
       </c>
       <c r="C4" t="n">
-        <v>38.8752455927652</v>
+        <v>37.94356702143497</v>
       </c>
       <c r="D4" t="n">
-        <v>41.38950146334128</v>
+        <v>49.46830332158828</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.54369260617026</v>
+        <v>30.704159450319</v>
       </c>
       <c r="C5" t="n">
-        <v>53.75068680751288</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D5" t="n">
-        <v>31.90680038802134</v>
+        <v>32.20132469929538</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.32958949118645</v>
+        <v>18.07299348747954</v>
       </c>
       <c r="C6" t="n">
-        <v>39.08435785376978</v>
+        <v>19.56230475482195</v>
       </c>
       <c r="D6" t="n">
-        <v>31.11452999069417</v>
+        <v>31.47679489356124</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.809001166028376</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>15.33097214951819</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.29182541453534</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>29.84218496599028</v>
       </c>
     </row>
     <row r="10">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>34.47308888692249</v>
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
         <v>32.11100391050467</v>
@@ -5916,7 +5916,7 @@
         <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.060092044191025</v>
+        <v>7.060252234987965</v>
       </c>
       <c r="C21" t="n">
-        <v>66.18836291429086</v>
+        <v>66.18986470301218</v>
       </c>
       <c r="D21" t="n">
-        <v>5.295069033143269</v>
+        <v>5.295189176240974</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.662319847468102</v>
+        <v>6.801548095021903</v>
       </c>
       <c r="C2" t="n">
-        <v>5.869869523691679</v>
+        <v>3.601050579177301</v>
       </c>
       <c r="D2" t="n">
-        <v>23.5462369386555</v>
+        <v>29.13630836663684</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.55994034878595</v>
+        <v>25.98195299289184</v>
       </c>
       <c r="C3" t="n">
-        <v>19.92947839621025</v>
+        <v>19.5613230071177</v>
       </c>
       <c r="D3" t="n">
-        <v>57.57950285407543</v>
+        <v>78.74598335763666</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.54569715930776</v>
+        <v>39.05392367493812</v>
       </c>
       <c r="C4" t="n">
-        <v>38.2881604656256</v>
+        <v>43.27838404631214</v>
       </c>
       <c r="D4" t="n">
-        <v>54.96903570848316</v>
+        <v>72.74750488468864</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.96217917008666</v>
+        <v>41.20885988575987</v>
       </c>
       <c r="C5" t="n">
-        <v>65.11441648416971</v>
+        <v>55.44420159733863</v>
       </c>
       <c r="D5" t="n">
-        <v>40.54618018539328</v>
+        <v>43.9086660724386</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.47929816831747</v>
+        <v>31.91956310817655</v>
       </c>
       <c r="C6" t="n">
-        <v>66.85800040691205</v>
+        <v>37.63529824230149</v>
       </c>
       <c r="D6" t="n">
-        <v>34.41516577237194</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.27675504160636</v>
+        <v>15.33097214951819</v>
       </c>
       <c r="C7" t="n">
-        <v>42.10028680121597</v>
+        <v>23.1162314441954</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>24.45042657426681</v>
+        <v>20.11110172149591</v>
       </c>
       <c r="D8" t="n">
         <v>32.21114217633784</v>
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.06249736236907</v>
       </c>
     </row>
     <row r="10">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.284990902108203</v>
+        <v>7.283711531126248</v>
       </c>
       <c r="C21" t="n">
-        <v>76.49240447213614</v>
+        <v>75.56850713543483</v>
       </c>
       <c r="D21" t="n">
-        <v>6.374367039344678</v>
+        <v>6.373247589735467</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.169482499936204</v>
+        <v>6.481498343437441</v>
       </c>
       <c r="C2" t="n">
-        <v>4.394302724208723</v>
+        <v>3.434153469455343</v>
       </c>
       <c r="D2" t="n">
-        <v>18.26836128062465</v>
+        <v>25.04732917844887</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.22967220953152</v>
+        <v>24.89221304117788</v>
       </c>
       <c r="C3" t="n">
-        <v>21.73589417202438</v>
+        <v>16.19392838155114</v>
       </c>
       <c r="D3" t="n">
-        <v>63.05765504377263</v>
+        <v>83.7823490804228</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.6425303291297</v>
+        <v>45.49909735331843</v>
       </c>
       <c r="C4" t="n">
-        <v>45.28213111067988</v>
+        <v>46.25209784247573</v>
       </c>
       <c r="D4" t="n">
-        <v>70.94796134280425</v>
+        <v>95.87355380592652</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.3680829402971</v>
+        <v>51.27177385428968</v>
       </c>
       <c r="C5" t="n">
-        <v>68.50144606382121</v>
+        <v>69.75317438673589</v>
       </c>
       <c r="D5" t="n">
-        <v>51.81173509162543</v>
+        <v>59.64117303299374</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.38749691020379</v>
+        <v>44.92084795551706</v>
       </c>
       <c r="C6" t="n">
-        <v>86.86307337634931</v>
+        <v>65.81145735418494</v>
       </c>
       <c r="D6" t="n">
-        <v>39.7686360036298</v>
+        <v>41.05668899160162</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.09815907489146</v>
+        <v>27.78738702100172</v>
       </c>
       <c r="C7" t="n">
-        <v>73.00177754008857</v>
+        <v>40.48334833232147</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="C8" t="n">
-        <v>42.14152020479433</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D8" t="n">
         <v>34.38080460272329</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>27.73437264497238</v>
+        <v>24.96093538047515</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>33.62976760897449</v>
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.498840257498391</v>
+        <v>7.495404307462025</v>
       </c>
       <c r="C21" t="n">
-        <v>86.2366629612315</v>
+        <v>85.26022399738054</v>
       </c>
       <c r="D21" t="n">
-        <v>7.498840257498391</v>
+        <v>7.495404307462025</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_87_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_87_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497604978966</v>
+        <v>10.84497645320096</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907095780465</v>
+        <v>37.78907236348209</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.772897485149498</v>
+        <v>8.103345550853172</v>
       </c>
       <c r="C2" t="n">
-        <v>4.088979188187965</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="D2" t="n">
-        <v>24.54761959698725</v>
+        <v>38.19293093831367</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.37541283811656</v>
+        <v>21.52972715413255</v>
       </c>
       <c r="C3" t="n">
-        <v>14.54950097693773</v>
+        <v>22.39857387239098</v>
       </c>
       <c r="D3" t="n">
-        <v>84.184865639164</v>
+        <v>83.87070637380502</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.67326760759762</v>
+        <v>40.86622993697772</v>
       </c>
       <c r="C4" t="n">
-        <v>42.65301075870693</v>
+        <v>70.62889333892403</v>
       </c>
       <c r="D4" t="n">
-        <v>115.1963121209122</v>
+        <v>112.4523272875424</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.54928965942204</v>
+        <v>48.52288028239862</v>
       </c>
       <c r="C5" t="n">
-        <v>78.2452920284708</v>
+        <v>98.73927535462298</v>
       </c>
       <c r="D5" t="n">
-        <v>78.78525326580655</v>
+        <v>81.90230222679017</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.47936458824226</v>
+        <v>42.14348370020284</v>
       </c>
       <c r="C6" t="n">
-        <v>89.31842438467058</v>
+        <v>105.7813516371854</v>
       </c>
       <c r="D6" t="n">
-        <v>50.27431818677493</v>
+        <v>53.13218575383738</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.32176087174825</v>
+        <v>27.48795397120644</v>
       </c>
       <c r="C7" t="n">
-        <v>68.21084874336412</v>
+        <v>85.51807902153115</v>
       </c>
       <c r="D7" t="n">
-        <v>39.82459562277186</v>
+        <v>41.26187426178919</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.02903582496668</v>
+        <v>14.77039421039326</v>
       </c>
       <c r="C8" t="n">
-        <v>40.55599766243574</v>
+        <v>51.23741268464103</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>29.28749751309084</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
         <v>34.27968458918587</v>
@@ -895,7 +895,7 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04009709162065</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
         <v>34.59188035913637</v>
@@ -909,7 +909,7 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -948,7 +948,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>23.35381438862312</v>
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.694466109130624</v>
+        <v>7.690804410039479</v>
       </c>
       <c r="C21" t="n">
-        <v>94.25720983685014</v>
+        <v>94.2123540229836</v>
       </c>
       <c r="D21" t="n">
-        <v>8.656274372771952</v>
+        <v>8.652154961294412</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.913688317484292</v>
+        <v>7.83925541841078</v>
       </c>
       <c r="C2" t="n">
-        <v>5.289656630481814</v>
+        <v>4.848851911274997</v>
       </c>
       <c r="D2" t="n">
-        <v>23.06223532046182</v>
+        <v>46.64970566269569</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.4384656753666</v>
+        <v>24.24916829489622</v>
       </c>
       <c r="C3" t="n">
-        <v>15.18272824617692</v>
+        <v>24.52405765208533</v>
       </c>
       <c r="D3" t="n">
-        <v>83.76762286485911</v>
+        <v>92.79479300540852</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.71606359595697</v>
+        <v>40.91728081759857</v>
       </c>
       <c r="C4" t="n">
-        <v>38.99011007416208</v>
+        <v>63.20099020859267</v>
       </c>
       <c r="D4" t="n">
-        <v>127.4995743505333</v>
+        <v>126.261590495478</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.91806694332035</v>
+        <v>54.11884219660543</v>
       </c>
       <c r="C5" t="n">
-        <v>78.417097876714</v>
+        <v>112.8028112179585</v>
       </c>
       <c r="D5" t="n">
-        <v>99.67193567365744</v>
+        <v>99.25469289935255</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>69.07184147998861</v>
+        <v>52.81017250684443</v>
       </c>
       <c r="C6" t="n">
-        <v>105.4995900460665</v>
+        <v>130.0531001292792</v>
       </c>
       <c r="D6" t="n">
-        <v>61.22276858453534</v>
+        <v>64.8856692690802</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>54.85613472249477</v>
+        <v>38.26754376383641</v>
       </c>
       <c r="C7" t="n">
-        <v>97.91460728305563</v>
+        <v>116.2997965404857</v>
       </c>
       <c r="D7" t="n">
-        <v>44.85507085933252</v>
+        <v>45.93302983859552</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.04424506661589</v>
+        <v>21.52972715413255</v>
       </c>
       <c r="C8" t="n">
-        <v>64.17193868809275</v>
+        <v>80.44440688598364</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.8656237377052</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>39.82655911818034</v>
+        <v>46.37187106239383</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>31.62994753542373</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1307,7 +1307,7 @@
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.880074168372414</v>
+        <v>7.871016716366435</v>
       </c>
       <c r="C21" t="n">
-        <v>103.4259734598879</v>
+        <v>102.3232173127637</v>
       </c>
       <c r="D21" t="n">
-        <v>9.850092710465518</v>
+        <v>9.838770895458042</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12.66356363707961</v>
+        <v>8.665886985386596</v>
       </c>
       <c r="C2" t="n">
-        <v>6.542366701100745</v>
+        <v>7.193265429016379</v>
       </c>
       <c r="D2" t="n">
-        <v>31.96668699798039</v>
+        <v>46.09698170520473</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.20208546282137</v>
+        <v>24.72040719293469</v>
       </c>
       <c r="C3" t="n">
-        <v>17.66654993792135</v>
+        <v>21.67208057124834</v>
       </c>
       <c r="D3" t="n">
-        <v>82.30972752405259</v>
+        <v>103.7069187381118</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.97957289132261</v>
+        <v>42.37223091529233</v>
       </c>
       <c r="C4" t="n">
-        <v>38.02014334236623</v>
+        <v>61.51631114810513</v>
       </c>
       <c r="D4" t="n">
-        <v>136.2675630971615</v>
+        <v>137.7608013553209</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>66.24342634405355</v>
+        <v>57.2849785428014</v>
       </c>
       <c r="C5" t="n">
-        <v>75.25096153051803</v>
+        <v>113.0482481440202</v>
       </c>
       <c r="D5" t="n">
-        <v>118.9878217547134</v>
+        <v>115.9444038715483</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>77.24292762243481</v>
+        <v>60.90075533754239</v>
       </c>
       <c r="C6" t="n">
-        <v>113.2279079738974</v>
+        <v>151.5474843660589</v>
       </c>
       <c r="D6" t="n">
-        <v>74.50581502299471</v>
+        <v>78.0882123957913</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>67.61198264377359</v>
+        <v>48.32849423695774</v>
       </c>
       <c r="C7" t="n">
-        <v>121.7494780467597</v>
+        <v>146.1233283000953</v>
       </c>
       <c r="D7" t="n">
-        <v>51.14316490503334</v>
+        <v>51.92169083450106</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>43.81049130201391</v>
+        <v>29.70768553050848</v>
       </c>
       <c r="C8" t="n">
-        <v>93.87962421860124</v>
+        <v>111.5707178491288</v>
       </c>
       <c r="D8" t="n">
-        <v>40.72289477215769</v>
+        <v>42.05807164993335</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22.2984356065578</v>
+        <v>15.30937370002476</v>
       </c>
       <c r="C9" t="n">
-        <v>57.243745139223</v>
+        <v>69.44686910301085</v>
       </c>
       <c r="D9" t="n">
-        <v>37.60780930658255</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.2494460323367</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>39.43189654107314</v>
+        <v>42.70602513473626</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>34.65078522139116</v>
+        <v>35.36157055926586</v>
       </c>
       <c r="D11" t="n">
-        <v>37.31623023842126</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.051925922115979</v>
+        <v>8.035017885756748</v>
       </c>
       <c r="C21" t="n">
-        <v>111.7204721693592</v>
+        <v>110.4814959291553</v>
       </c>
       <c r="D21" t="n">
-        <v>11.07139814290947</v>
+        <v>11.04814959291553</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11.34016773175491</v>
+        <v>8.037568454668637</v>
       </c>
       <c r="C2" t="n">
-        <v>4.343251843587889</v>
+        <v>4.891067062557609</v>
       </c>
       <c r="D2" t="n">
-        <v>25.94955531865169</v>
+        <v>37.8728811867292</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>34.30226478638355</v>
+        <v>29.46715734296801</v>
       </c>
       <c r="C3" t="n">
-        <v>27.16005023798801</v>
+        <v>34.88640467041041</v>
       </c>
       <c r="D3" t="n">
-        <v>92.73097940463248</v>
+        <v>110.8540420250286</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.81746134693488</v>
+        <v>27.5164246546296</v>
       </c>
       <c r="C4" t="n">
-        <v>59.09139431861551</v>
+        <v>90.09204157561705</v>
       </c>
       <c r="D4" t="n">
-        <v>132.4259843304438</v>
+        <v>131.5964075203552</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.51596699073988</v>
+        <v>34.31208226342603</v>
       </c>
       <c r="C5" t="n">
-        <v>67.64241682260524</v>
+        <v>90.5416820241621</v>
       </c>
       <c r="D5" t="n">
-        <v>77.63169971331654</v>
+        <v>77.8280492541659</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.98247707670636</v>
+        <v>29.98748362621883</v>
       </c>
       <c r="C6" t="n">
-        <v>80.18129850124551</v>
+        <v>96.24170919501908</v>
       </c>
       <c r="D6" t="n">
-        <v>33.65038431076368</v>
+        <v>34.17365583712723</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.04500583014188</v>
+        <v>19.64280806657018</v>
       </c>
       <c r="C7" t="n">
-        <v>65.99504417487908</v>
+        <v>78.45145904636261</v>
       </c>
       <c r="D7" t="n">
-        <v>28.62579956042849</v>
+        <v>29.52409870981433</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.43798264928109</v>
+        <v>10.59796646734432</v>
       </c>
       <c r="C8" t="n">
-        <v>42.14152020479433</v>
+        <v>51.15396412978005</v>
       </c>
       <c r="D8" t="n">
-        <v>27.70492021384499</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>30.06405994715006</v>
+        <v>32.61562223048752</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.27567548291088</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.704355072301468</v>
+        <v>4.825289966373073</v>
       </c>
       <c r="C2" t="n">
-        <v>2.215804568485051</v>
+        <v>2.655627539987622</v>
       </c>
       <c r="D2" t="n">
-        <v>18.06710300125405</v>
+        <v>26.70844629403447</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>37.75310796681109</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="C3" t="n">
-        <v>22.24149423971149</v>
+        <v>27.58711048933537</v>
       </c>
       <c r="D3" t="n">
-        <v>93.45747270577512</v>
+        <v>115.1442794925872</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.41350537659971</v>
+        <v>39.76863600362979</v>
       </c>
       <c r="C4" t="n">
-        <v>65.65143247839271</v>
+        <v>91.08753374772331</v>
       </c>
       <c r="D4" t="n">
-        <v>146.3628747399315</v>
+        <v>154.1736594749191</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.71293842639499</v>
+        <v>38.85266539556753</v>
       </c>
       <c r="C5" t="n">
-        <v>88.25911861178827</v>
+        <v>127.136327699962</v>
       </c>
       <c r="D5" t="n">
-        <v>101.2918193856647</v>
+        <v>98.81290643244149</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.47557646614552</v>
+        <v>35.783722072092</v>
       </c>
       <c r="C6" t="n">
-        <v>96.24170919501908</v>
+        <v>119.2254046991412</v>
       </c>
       <c r="D6" t="n">
-        <v>43.19002675292993</v>
+        <v>43.71329827929349</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.42806736124739</v>
+        <v>18.50496247734813</v>
       </c>
       <c r="C7" t="n">
-        <v>86.89547105058944</v>
+        <v>103.0648557395344</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>32.33876937788993</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.76762889372977</v>
+        <v>8.92899537012474</v>
       </c>
       <c r="C8" t="n">
-        <v>56.74501730546564</v>
+        <v>68.51126354086365</v>
       </c>
       <c r="D8" t="n">
-        <v>28.87319998189869</v>
+        <v>28.28906009787184</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>35.94374694788421</v>
+        <v>37.60780930658255</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2142,7 +2142,7 @@
         <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
+        <v>29.14219885286231</v>
+      </c>
+      <c r="D11" t="n">
         <v>29.67528785626833</v>
-      </c>
-      <c r="D11" t="n">
-        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2170,7 +2170,7 @@
         <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
         <v>18.74450891718435</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.693956758182253</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C2" t="n">
-        <v>5.53411180883927</v>
+        <v>4.298091449192536</v>
       </c>
       <c r="D2" t="n">
-        <v>29.87654613563893</v>
+        <v>21.86548486898496</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.12983704333461</v>
+        <v>22.84036033930204</v>
       </c>
       <c r="C3" t="n">
-        <v>14.8194815956056</v>
+        <v>18.49612674800991</v>
       </c>
       <c r="D3" t="n">
-        <v>86.57542129900497</v>
+        <v>110.9767604880595</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>59.79334392715199</v>
+        <v>48.03887866420492</v>
       </c>
       <c r="C4" t="n">
-        <v>60.30385273336033</v>
+        <v>79.7031873692773</v>
       </c>
       <c r="D4" t="n">
-        <v>158.6023233687765</v>
+        <v>173.1773497860246</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.61662934038758</v>
+        <v>48.37561812676159</v>
       </c>
       <c r="C5" t="n">
-        <v>105.0224606618026</v>
+        <v>147.0658060961722</v>
       </c>
       <c r="D5" t="n">
-        <v>127.6026578594792</v>
+        <v>126.1545799957152</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.51961624411638</v>
+        <v>43.31078172055229</v>
       </c>
       <c r="C6" t="n">
-        <v>118.9838947638964</v>
+        <v>159.4770605732604</v>
       </c>
       <c r="D6" t="n">
-        <v>61.46427851978007</v>
+        <v>60.17622553180826</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.32176087174825</v>
+        <v>28.32636651063322</v>
       </c>
       <c r="C7" t="n">
-        <v>113.0659196026967</v>
+        <v>136.0623778269739</v>
       </c>
       <c r="D7" t="n">
-        <v>35.75230614555609</v>
+        <v>36.47094546506476</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.27661617288612</v>
+        <v>13.01797455831271</v>
       </c>
       <c r="C8" t="n">
-        <v>84.36648896444964</v>
+        <v>99.30378028456487</v>
       </c>
       <c r="D8" t="n">
-        <v>30.54217107911827</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.098436812331936</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>51.69687061022852</v>
+        <v>57.79843259212245</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.989421759431538</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>36.86953503298896</v>
+        <v>37.29659528433633</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.60598467989432</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.485605260703677</v>
+        <v>2.997275741065512</v>
       </c>
       <c r="C2" t="n">
-        <v>2.490693925674158</v>
+        <v>2.02534551386117</v>
       </c>
       <c r="D2" t="n">
-        <v>20.60884780754904</v>
+        <v>15.30151971839079</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>31.35702167364312</v>
+        <v>22.57037972063417</v>
       </c>
       <c r="C3" t="n">
-        <v>18.84464718301752</v>
+        <v>18.76119862815655</v>
       </c>
       <c r="D3" t="n">
-        <v>91.52833846693014</v>
+        <v>108.3162242095506</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>66.11089040398021</v>
+        <v>52.65898336039042</v>
       </c>
       <c r="C4" t="n">
-        <v>57.30461349688632</v>
+        <v>75.83608316224911</v>
       </c>
       <c r="D4" t="n">
-        <v>167.7659564402162</v>
+        <v>186.8206976319426</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.66004722355269</v>
+        <v>49.40645321622075</v>
       </c>
       <c r="C5" t="n">
-        <v>121.5894531709675</v>
+        <v>169.8423528346982</v>
       </c>
       <c r="D5" t="n">
-        <v>137.8619213688584</v>
+        <v>133.4440566997477</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.07305990740432</v>
+        <v>35.17994723398021</v>
       </c>
       <c r="C6" t="n">
-        <v>148.6493651431223</v>
+        <v>191.0343587785699</v>
       </c>
       <c r="D6" t="n">
-        <v>59.8542122848153</v>
+        <v>58.48565598509524</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.75584792127881</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>117.2579822998305</v>
+        <v>138.1584091755409</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>65.34021845614646</v>
+        <v>73.68507394224434</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>31.62700229231099</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>28.06718511671205</v>
+        <v>28.39999758845172</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>25.33890824661018</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.500732386894879</v>
+        <v>3.734568266954867</v>
       </c>
       <c r="C2" t="n">
-        <v>2.114684554947629</v>
+        <v>6.609125544989528</v>
       </c>
       <c r="D2" t="n">
-        <v>19.41602434688917</v>
+        <v>16.59840843570083</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.47358760854124</v>
+        <v>16.64553232550467</v>
       </c>
       <c r="C3" t="n">
-        <v>14.04390090925062</v>
+        <v>13.233959053247</v>
       </c>
       <c r="D3" t="n">
-        <v>87.76333602114362</v>
+        <v>96.70705760683205</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>63.95399069774997</v>
+        <v>48.20479402622264</v>
       </c>
       <c r="C4" t="n">
-        <v>52.03361007278519</v>
+        <v>61.52907386826035</v>
       </c>
       <c r="D4" t="n">
-        <v>174.12179107751</v>
+        <v>198.3964848127167</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>78.85888434362505</v>
+        <v>62.09554229361077</v>
       </c>
       <c r="C5" t="n">
-        <v>114.8644813968768</v>
+        <v>157.1041763720958</v>
       </c>
       <c r="D5" t="n">
-        <v>162.0374585859361</v>
+        <v>161.8901964302991</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.16113946334606</v>
+        <v>47.65796055495717</v>
       </c>
       <c r="C6" t="n">
-        <v>171.0695374650067</v>
+        <v>228.1061338386337</v>
       </c>
       <c r="D6" t="n">
-        <v>83.56243759467154</v>
+        <v>79.25551041614078</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.98511922018283</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="C7" t="n">
-        <v>163.2508987483851</v>
+        <v>199.4822977736137</v>
       </c>
       <c r="D7" t="n">
-        <v>42.22006002113408</v>
+        <v>42.57937968088841</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.094509821514951</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>104.0603479116407</v>
+        <v>118.1631536831461</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>33.54631905411351</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>49.03437083631118</v>
+        <v>51.69687061022852</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>24.16670148773948</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.60978849752428</v>
+      </c>
+      <c r="D13" t="n">
         <v>15.86995163914969</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.223478623669778</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C2" t="n">
-        <v>1.461822331623501</v>
+        <v>4.32754388031994</v>
       </c>
       <c r="D2" t="n">
-        <v>14.9431818063407</v>
+        <v>12.46917759163874</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.73589417202438</v>
+        <v>15.15327581504952</v>
       </c>
       <c r="C3" t="n">
-        <v>11.388273369263</v>
+        <v>19.13426275577033</v>
       </c>
       <c r="D3" t="n">
-        <v>84.88190650917923</v>
+        <v>89.79555376893451</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>58.04485126588842</v>
+        <v>42.67853619901734</v>
       </c>
       <c r="C4" t="n">
-        <v>45.74158903626739</v>
+        <v>50.82115165804039</v>
       </c>
       <c r="D4" t="n">
-        <v>177.7591663217445</v>
+        <v>201.3957240491907</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>87.0810213666921</v>
+        <v>68.05965959691014</v>
       </c>
       <c r="C5" t="n">
-        <v>111.1829275059513</v>
+        <v>145.7159030028328</v>
       </c>
       <c r="D5" t="n">
-        <v>178.5553637098887</v>
+        <v>185.378510254404</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>77.08192099893833</v>
+        <v>56.75483478250812</v>
       </c>
       <c r="C6" t="n">
-        <v>183.8695640329767</v>
+        <v>246.782902164225</v>
       </c>
       <c r="D6" t="n">
-        <v>102.4807158555076</v>
+        <v>95.91969594802613</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.26647990067416</v>
+        <v>17.96598298771663</v>
       </c>
       <c r="C7" t="n">
-        <v>198.5241120142688</v>
+        <v>247.3316991308989</v>
       </c>
       <c r="D7" t="n">
-        <v>48.32849423695774</v>
+        <v>48.92736033654828</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.508987279156353</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>136.0211444233956</v>
+        <v>155.0474149316988</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>34.63115026730623</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>60.57186985661969</v>
+        <v>61.23749480009903</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
         <v>24.34439782220815</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.244897146713961</v>
+        <v>3.942698780255191</v>
       </c>
       <c r="C2" t="n">
-        <v>10.73933813675586</v>
+        <v>10.42223362828414</v>
       </c>
       <c r="D2" t="n">
-        <v>14.76548547187203</v>
+        <v>15.44681837861931</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.06906649666254</v>
+        <v>12.13440162449058</v>
       </c>
       <c r="C3" t="n">
-        <v>8.541205026947251</v>
+        <v>17.89235190989812</v>
       </c>
       <c r="D3" t="n">
-        <v>78.00967257945155</v>
+        <v>80.75365741282138</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.940523967331</v>
+        <v>36.08020987877453</v>
       </c>
       <c r="C4" t="n">
-        <v>37.50963453615788</v>
+        <v>49.28962523941536</v>
       </c>
       <c r="D4" t="n">
-        <v>178.9460992961789</v>
+        <v>199.8897230708761</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>88.13640014875742</v>
+        <v>67.15154297048184</v>
       </c>
       <c r="C5" t="n">
-        <v>98.83745012504767</v>
+        <v>122.8657251864883</v>
       </c>
       <c r="D5" t="n">
-        <v>196.61952146803</v>
+        <v>206.8787849774092</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>93.38384162795661</v>
+        <v>69.19259644761097</v>
       </c>
       <c r="C6" t="n">
-        <v>181.5752196481519</v>
+        <v>243.9652862530367</v>
       </c>
       <c r="D6" t="n">
-        <v>126.7122126917273</v>
+        <v>119.7084245696306</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>50.84373185523806</v>
+        <v>35.03366682604743</v>
       </c>
       <c r="C7" t="n">
-        <v>230.5035617324044</v>
+        <v>291.8274503304771</v>
       </c>
       <c r="D7" t="n">
-        <v>61.08434215823654</v>
+        <v>60.36570283872788</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.35315143608837</v>
+        <v>9.095892479846697</v>
       </c>
       <c r="C8" t="n">
-        <v>188.2599397663683</v>
+        <v>221.8062588204818</v>
       </c>
       <c r="D8" t="n">
-        <v>39.38771789438203</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.439062207976575</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>103.5046787110369</v>
+        <v>110.0499906552504</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>46.83427423109409</v>
+        <v>45.26838664282043</v>
       </c>
       <c r="D10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
         <v>24.87748682561417</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.252972112526189</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C2" t="n">
-        <v>2.974695543867836</v>
+        <v>3.431208226342602</v>
       </c>
       <c r="D2" t="n">
-        <v>12.19428823444963</v>
+        <v>19.47198396603124</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.37663126553228</v>
+        <v>2.82252464970958</v>
       </c>
       <c r="C2" t="n">
-        <v>5.927792638242241</v>
+        <v>5.91895690890402</v>
       </c>
       <c r="D2" t="n">
-        <v>10.75013736150257</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.36697801940583</v>
+        <v>16.44427404613408</v>
       </c>
       <c r="C3" t="n">
-        <v>20.44980467946106</v>
+        <v>27.37603473292231</v>
       </c>
       <c r="D3" t="n">
-        <v>84.16523068507905</v>
+        <v>87.63080008107029</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>67.88490850555419</v>
+        <v>50.65523629602267</v>
       </c>
       <c r="C4" t="n">
-        <v>53.57789921156542</v>
+        <v>71.85411447382405</v>
       </c>
       <c r="D4" t="n">
-        <v>185.0339168102133</v>
+        <v>203.2463184716959</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.67138622764714</v>
+        <v>40.84070449666732</v>
       </c>
       <c r="C5" t="n">
-        <v>149.9619618237003</v>
+        <v>196.8158710088794</v>
       </c>
       <c r="D5" t="n">
-        <v>180.5434028109885</v>
+        <v>186.7038696551372</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.55729820530948</v>
+        <v>21.73589417202438</v>
       </c>
       <c r="C6" t="n">
-        <v>192.7249283252829</v>
+        <v>240.020623977373</v>
       </c>
       <c r="D6" t="n">
-        <v>97.93227874173209</v>
+        <v>93.22283500446015</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>5.988660995905543</v>
       </c>
       <c r="C7" t="n">
-        <v>132.3494080095125</v>
+        <v>155.9447323333803</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05173919535137</v>
+        <v>34.55457394637499</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.336559536107409</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>76.2719791429347</v>
+        <v>81.11199532487147</v>
       </c>
       <c r="D8" t="n">
-        <v>25.03456645829366</v>
+        <v>24.95111790343269</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>35.72187196672443</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>20.52343575727956</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.34948648717864</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
         <v>19.50241814486289</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8811517745239</v>
+        <v>16.17036643664921</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.17795837637593</v>
+        <v>5.781512230309467</v>
       </c>
       <c r="C2" t="n">
-        <v>2.347358760854124</v>
+        <v>4.420809912223387</v>
       </c>
       <c r="D2" t="n">
-        <v>16.94889236611693</v>
+        <v>19.45038551653781</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.63986282345744</v>
+        <v>11.79569866652543</v>
       </c>
       <c r="C3" t="n">
-        <v>7.495643721924397</v>
+        <v>8.644288535893166</v>
       </c>
       <c r="D3" t="n">
-        <v>13.38122120888403</v>
+        <v>19.49260066782042</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39780937749015</v>
+        <v>13.39711800594602</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1414726233308</v>
+        <v>70.1378530899527</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576212867940018</v>
+        <v>1.576131530111296</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.227225688037517</v>
+        <v>4.055599766243573</v>
       </c>
       <c r="C2" t="n">
-        <v>5.592034923389832</v>
+        <v>6.977280934082081</v>
       </c>
       <c r="D2" t="n">
-        <v>21.19691468239288</v>
+        <v>20.85232123820225</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.87748682561417</v>
+        <v>16.71425466480195</v>
       </c>
       <c r="C3" t="n">
-        <v>8.531387549904784</v>
+        <v>14.01935721664445</v>
       </c>
       <c r="D3" t="n">
-        <v>24.38170423496954</v>
+        <v>31.12140222462389</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.61554011502952</v>
+        <v>13.7582123273148</v>
       </c>
       <c r="C4" t="n">
-        <v>11.98419422574081</v>
+        <v>13.73268688700438</v>
       </c>
       <c r="D4" t="n">
-        <v>22.07950586851077</v>
+        <v>25.28294862746811</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.092505268377454</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.448699758569798</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -4896,7 +4896,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44108937286551</v>
+        <v>15.44001395203293</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14502492230231</v>
+        <v>86.13902520607847</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25075565744537</v>
+        <v>3.250529253059565</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.51331518060084</v>
+        <v>6.028912651779663</v>
       </c>
       <c r="C2" t="n">
-        <v>7.086254929253477</v>
+        <v>5.972953032637593</v>
       </c>
       <c r="D2" t="n">
-        <v>33.37353145816607</v>
+        <v>30.90934472050658</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.01216618754523</v>
+        <v>15.20727193878309</v>
       </c>
       <c r="C3" t="n">
-        <v>16.55226629360122</v>
+        <v>21.98133109808609</v>
       </c>
       <c r="D3" t="n">
-        <v>35.68162031085032</v>
+        <v>40.58054135504191</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.01188845010475</v>
+        <v>24.23640557474101</v>
       </c>
       <c r="C4" t="n">
-        <v>17.51045205294611</v>
+        <v>26.30396623988479</v>
       </c>
       <c r="D4" t="n">
-        <v>29.32873091666921</v>
+        <v>35.18681946790993</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.315886081056</v>
+        <v>12.34547738090364</v>
       </c>
       <c r="C5" t="n">
-        <v>14.94710879715769</v>
+        <v>16.73879835740812</v>
       </c>
       <c r="D5" t="n">
-        <v>30.36054775383262</v>
+        <v>31.48955761371645</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
         <v>36.8302651248191</v>
@@ -5207,7 +5207,7 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
         <v>37.24947139453248</v>
@@ -5221,7 +5221,7 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
         <v>38.38633523605029</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.736136952021</v>
+        <v>16.73520749277658</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0904354073281</v>
+        <v>102.0847657059372</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020841085606299</v>
+        <v>5.020562247832975</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.123561342014856</v>
+        <v>6.944883259841937</v>
       </c>
       <c r="C2" t="n">
-        <v>4.428663893857362</v>
+        <v>6.998879383575511</v>
       </c>
       <c r="D2" t="n">
-        <v>35.41654843070368</v>
+        <v>27.57827475999715</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.51424017504286</v>
+        <v>18.19669369821463</v>
       </c>
       <c r="C3" t="n">
-        <v>22.85999529338698</v>
+        <v>22.66364575253762</v>
       </c>
       <c r="D3" t="n">
-        <v>53.10764206123121</v>
+        <v>55.04168503859743</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.30016242225481</v>
+        <v>27.18459393059418</v>
       </c>
       <c r="C4" t="n">
-        <v>30.86025733529424</v>
+        <v>42.07868835172254</v>
       </c>
       <c r="D4" t="n">
-        <v>39.99836496642355</v>
+        <v>46.94128473085699</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.28186906877263</v>
+        <v>24.24916829489622</v>
       </c>
       <c r="C5" t="n">
-        <v>24.20008090968388</v>
+        <v>34.23845118560752</v>
       </c>
       <c r="D5" t="n">
-        <v>33.62485887045326</v>
+        <v>36.47192721276901</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.02015903789946</v>
+        <v>11.39121861237574</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>19.80381469006666</v>
       </c>
       <c r="D6" t="n">
-        <v>38.56108632740622</v>
+        <v>38.84284791852506</v>
       </c>
     </row>
     <row r="7">
@@ -5518,7 +5518,7 @@
         <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
         <v>39.40538935305847</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.79389940203295</v>
       </c>
       <c r="D8" t="n">
         <v>40.22220344299182</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
         <v>41.82343394861835</v>
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5574,7 +5574,7 @@
         <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06292647917194</v>
+        <v>18.06290434007563</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8390917926931</v>
+        <v>117.8389473614458</v>
       </c>
       <c r="D21" t="n">
-        <v>6.881114849208356</v>
+        <v>6.881106415266908</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.146542449840032</v>
+        <v>7.082327938436491</v>
       </c>
       <c r="C2" t="n">
-        <v>5.154175447295755</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="D2" t="n">
-        <v>34.88345942729767</v>
+        <v>31.92839883751477</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.75552912610932</v>
+        <v>19.00663555421825</v>
       </c>
       <c r="C3" t="n">
-        <v>18.42740440871263</v>
+        <v>23.72393327312417</v>
       </c>
       <c r="D3" t="n">
-        <v>64.17193868809277</v>
+        <v>59.98478472948011</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.36625831360885</v>
+        <v>22.93460811890974</v>
       </c>
       <c r="C4" t="n">
-        <v>37.94356702143497</v>
+        <v>41.75962034784233</v>
       </c>
       <c r="D4" t="n">
-        <v>49.46830332158828</v>
+        <v>54.63720498444773</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.704159450319</v>
+        <v>19.9785657814226</v>
       </c>
       <c r="C5" t="n">
-        <v>31.31775176547326</v>
+        <v>43.12326790904115</v>
       </c>
       <c r="D5" t="n">
-        <v>32.20132469929538</v>
+        <v>36.61918936840603</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.07299348747954</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="C6" t="n">
-        <v>19.56230475482195</v>
+        <v>25.51954982419159</v>
       </c>
       <c r="D6" t="n">
-        <v>31.47679489356124</v>
+        <v>32.28182801104362</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.886960145291375</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>15.33097214951819</v>
+        <v>16.16938468894497</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5871,7 +5871,7 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
         <v>34.47308888692249</v>
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>32.11100391050467</v>
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.060252234987965</v>
+        <v>7.060914526761252</v>
       </c>
       <c r="C21" t="n">
-        <v>66.18986470301218</v>
+        <v>66.19607368838673</v>
       </c>
       <c r="D21" t="n">
-        <v>5.295189176240974</v>
+        <v>5.295685895070939</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.801548095021903</v>
+        <v>6.458918146239766</v>
       </c>
       <c r="C2" t="n">
-        <v>3.601050579177301</v>
+        <v>8.883834975729387</v>
       </c>
       <c r="D2" t="n">
-        <v>29.13630836663684</v>
+        <v>31.96963224109313</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.98195299289184</v>
+        <v>22.62437584436775</v>
       </c>
       <c r="C3" t="n">
-        <v>19.5613230071177</v>
+        <v>26.52682296874882</v>
       </c>
       <c r="D3" t="n">
-        <v>78.74598335763666</v>
+        <v>73.58689917181968</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.05392367493812</v>
+        <v>31.88127494771092</v>
       </c>
       <c r="C4" t="n">
-        <v>43.27838404631214</v>
+        <v>53.13120400613313</v>
       </c>
       <c r="D4" t="n">
-        <v>72.74750488468864</v>
+        <v>72.87513208624073</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.20885988575987</v>
+        <v>28.37250865273283</v>
       </c>
       <c r="C5" t="n">
-        <v>55.44420159733863</v>
+        <v>64.35356201337844</v>
       </c>
       <c r="D5" t="n">
-        <v>43.9086660724386</v>
+        <v>49.2837347531899</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.91956310817655</v>
+        <v>21.01136436629024</v>
       </c>
       <c r="C6" t="n">
-        <v>37.63529824230149</v>
+        <v>51.20010627187966</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>36.8302651248191</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.33097214951819</v>
+        <v>10.83947640258903</v>
       </c>
       <c r="C7" t="n">
-        <v>23.1162314441954</v>
+        <v>28.50602634051038</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>33.83593462686632</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.508987279156353</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>20.11110172149591</v>
+        <v>20.69524160552276</v>
       </c>
       <c r="D8" t="n">
         <v>32.21114217633784</v>
@@ -6182,7 +6182,7 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
         <v>34.16482010778901</v>
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>31.21957699504857</v>
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.283711531126248</v>
+        <v>7.284179911745652</v>
       </c>
       <c r="C21" t="n">
-        <v>75.56850713543483</v>
+        <v>75.57336658436115</v>
       </c>
       <c r="D21" t="n">
-        <v>6.373247589735467</v>
+        <v>6.373657422777446</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.481498343437441</v>
+        <v>5.975898275750335</v>
       </c>
       <c r="C2" t="n">
-        <v>3.434153469455343</v>
+        <v>4.015348110369454</v>
       </c>
       <c r="D2" t="n">
-        <v>25.04732917844887</v>
+        <v>26.37170683147782</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.89221304117788</v>
+        <v>22.48693116577319</v>
       </c>
       <c r="C3" t="n">
-        <v>16.19392838155114</v>
+        <v>31.40610905885546</v>
       </c>
       <c r="D3" t="n">
-        <v>83.7823490804228</v>
+        <v>82.08883429059705</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.49909735331843</v>
+        <v>38.67104207028186</v>
       </c>
       <c r="C4" t="n">
-        <v>46.25209784247573</v>
+        <v>60.99303962174159</v>
       </c>
       <c r="D4" t="n">
-        <v>95.87355380592652</v>
+        <v>93.39758609581605</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.27177385428968</v>
+        <v>39.22082078466008</v>
       </c>
       <c r="C5" t="n">
-        <v>69.75317438673589</v>
+        <v>83.08039947188634</v>
       </c>
       <c r="D5" t="n">
-        <v>59.64117303299374</v>
+        <v>63.86268816125503</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.92084795551706</v>
+        <v>30.43025184083414</v>
       </c>
       <c r="C6" t="n">
-        <v>65.81145735418494</v>
+        <v>79.81903359837844</v>
       </c>
       <c r="D6" t="n">
-        <v>41.05668899160162</v>
+        <v>44.31707311740527</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.78738702100172</v>
+        <v>18.68462230722529</v>
       </c>
       <c r="C7" t="n">
-        <v>40.48334833232147</v>
+        <v>53.71828913327272</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05173919535137</v>
+        <v>36.83026512481909</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.93314334511998</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>26.03594911662541</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>24.96093538047515</v>
+        <v>25.4046853427947</v>
       </c>
       <c r="D9" t="n">
         <v>32.61562223048752</v>
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
         <v>34.30717352490479</v>
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
         <v>33.62976760897449</v>
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>32.00006641992479</v>
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.495404307462025</v>
+        <v>7.494432634130789</v>
       </c>
       <c r="C21" t="n">
-        <v>85.26022399738054</v>
+        <v>85.24917121323772</v>
       </c>
       <c r="D21" t="n">
-        <v>7.495404307462025</v>
+        <v>7.494432634130789</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_87_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_87_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497645320096</v>
+        <v>10.84497618244128</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907236348209</v>
+        <v>37.7890714200262</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.103345550853172</v>
+        <v>1.336158625479909</v>
       </c>
       <c r="C2" t="n">
-        <v>6.886960145291375</v>
+        <v>2.237403017978481</v>
       </c>
       <c r="D2" t="n">
-        <v>38.19293093831367</v>
+        <v>14.81555460478862</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.52972715413255</v>
+        <v>11.44226949299657</v>
       </c>
       <c r="C3" t="n">
-        <v>22.39857387239098</v>
+        <v>22.58510593619787</v>
       </c>
       <c r="D3" t="n">
-        <v>83.87070637380502</v>
+        <v>63.946136716116</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.86622993697772</v>
+        <v>20.26719960647115</v>
       </c>
       <c r="C4" t="n">
-        <v>70.62889333892403</v>
+        <v>74.22798042269284</v>
       </c>
       <c r="D4" t="n">
-        <v>112.4523272875424</v>
+        <v>74.06206506067512</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.52288028239862</v>
+        <v>20.69033286700153</v>
       </c>
       <c r="C5" t="n">
-        <v>98.73927535462298</v>
+        <v>81.2150788338174</v>
       </c>
       <c r="D5" t="n">
-        <v>81.90230222679017</v>
+        <v>47.44295780772712</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.14348370020284</v>
+        <v>14.20883452356409</v>
       </c>
       <c r="C6" t="n">
-        <v>105.7813516371854</v>
+        <v>54.25923211831272</v>
       </c>
       <c r="D6" t="n">
-        <v>53.13218575383738</v>
+        <v>30.51075515258238</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.48795397120644</v>
+        <v>6.587527095496098</v>
       </c>
       <c r="C7" t="n">
-        <v>85.51807902153115</v>
+        <v>35.87207936547421</v>
       </c>
       <c r="D7" t="n">
-        <v>41.26187426178919</v>
+        <v>29.88341836956866</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.77039421039326</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>51.23741268464103</v>
+        <v>28.78975142703771</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>30.87596529856218</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.543749359432489</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>31.8390597964283</v>
+        <v>32.50468473990763</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>38.15071578703105</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>31.62994753542373</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.690804410039479</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.2123540229836</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.652154961294412</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.83925541841078</v>
+        <v>1.045561305022853</v>
       </c>
       <c r="C2" t="n">
-        <v>4.848851911274997</v>
+        <v>2.66839026014283</v>
       </c>
       <c r="D2" t="n">
-        <v>46.64970566269569</v>
+        <v>17.10989898961341</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.24916829489622</v>
+        <v>7.687084524252525</v>
       </c>
       <c r="C3" t="n">
-        <v>24.52405765208533</v>
+        <v>14.25497666566369</v>
       </c>
       <c r="D3" t="n">
-        <v>92.79479300540852</v>
+        <v>60.96162369520569</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.91728081759857</v>
+        <v>21.65833610338889</v>
       </c>
       <c r="C4" t="n">
-        <v>63.20099020859267</v>
+        <v>63.89017709697393</v>
       </c>
       <c r="D4" t="n">
-        <v>126.261590495478</v>
+        <v>89.50495644847746</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.11884219660543</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="C5" t="n">
-        <v>112.8028112179585</v>
+        <v>113.9563647704485</v>
       </c>
       <c r="D5" t="n">
-        <v>99.25469289935255</v>
+        <v>63.32272692391928</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.81017250684443</v>
+        <v>21.29312595740907</v>
       </c>
       <c r="C6" t="n">
-        <v>130.0531001292792</v>
+        <v>95.07441117466963</v>
       </c>
       <c r="D6" t="n">
-        <v>64.8856692690802</v>
+        <v>38.23907308041327</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.26754376383641</v>
+        <v>11.43834250217959</v>
       </c>
       <c r="C7" t="n">
-        <v>116.2997965404857</v>
+        <v>58.56910453995621</v>
       </c>
       <c r="D7" t="n">
-        <v>45.93302983859552</v>
+        <v>32.39865598784899</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.52972715413255</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>80.44440688598364</v>
+        <v>39.30426933952106</v>
       </c>
       <c r="D8" t="n">
-        <v>39.05392367493811</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>46.37187106239383</v>
+        <v>35.27812200440487</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>33.88011327355743</v>
+        <v>35.44600086183109</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>38.57777603837842</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>31.62994753542373</v>
+        <v>34.82848155585983</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>29.50740899884213</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>38.61999118966103</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.27040689149115</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.871016716366435</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>102.3232173127637</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.838770895458042</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.665886985386596</v>
+        <v>0.5478152189697202</v>
       </c>
       <c r="C2" t="n">
-        <v>7.193265429016379</v>
+        <v>1.085812960896972</v>
       </c>
       <c r="D2" t="n">
-        <v>46.09698170520473</v>
+        <v>11.54437125423824</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.72040719293469</v>
+        <v>6.675884388878311</v>
       </c>
       <c r="C3" t="n">
-        <v>21.67208057124834</v>
+        <v>13.24377653028947</v>
       </c>
       <c r="D3" t="n">
-        <v>103.7069187381118</v>
+        <v>62.44897146713961</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.37223091529233</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="C4" t="n">
-        <v>61.51631114810513</v>
+        <v>57.61091878061133</v>
       </c>
       <c r="D4" t="n">
-        <v>137.7608013553209</v>
+        <v>99.02594568426302</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.2849785428014</v>
+        <v>26.77716863333176</v>
       </c>
       <c r="C5" t="n">
-        <v>113.0482481440202</v>
+        <v>130.6460757426443</v>
       </c>
       <c r="D5" t="n">
-        <v>115.9444038715483</v>
+        <v>72.52661165123313</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.90075533754239</v>
+        <v>16.98619877887832</v>
       </c>
       <c r="C6" t="n">
-        <v>151.5474843660589</v>
+        <v>127.9197623679509</v>
       </c>
       <c r="D6" t="n">
-        <v>78.0882123957913</v>
+        <v>39.16486116551801</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.32849423695774</v>
+        <v>4.73104218676538</v>
       </c>
       <c r="C7" t="n">
-        <v>146.1233283000953</v>
+        <v>60.18604300885071</v>
       </c>
       <c r="D7" t="n">
-        <v>51.92169083450106</v>
+        <v>34.01559445674349</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.70768553050848</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>111.5707178491288</v>
+        <v>40.63944621729671</v>
       </c>
       <c r="D8" t="n">
-        <v>42.05807164993335</v>
+        <v>36.71736413883071</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.30937370002476</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>69.44686910301085</v>
+        <v>27.06874770149305</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.114144775599888</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>42.70602513473626</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>35.36157055926586</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.91916219754903</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.41468274628643</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>18.74450891718435</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.035017885756748</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110.4814959291553</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.04814959291553</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.037568454668637</v>
+        <v>0.7412195167063418</v>
       </c>
       <c r="C2" t="n">
-        <v>4.891067062557609</v>
+        <v>2.873575530330414</v>
       </c>
       <c r="D2" t="n">
-        <v>37.8728811867292</v>
+        <v>10.65098084337365</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.46715734296801</v>
+        <v>4.118431619315369</v>
       </c>
       <c r="C3" t="n">
-        <v>34.88640467041041</v>
+        <v>7.898160280665589</v>
       </c>
       <c r="D3" t="n">
-        <v>110.8540420250286</v>
+        <v>57.79548734900973</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.5164246546296</v>
+        <v>18.27621526225862</v>
       </c>
       <c r="C4" t="n">
-        <v>90.09204157561705</v>
+        <v>44.05690997577986</v>
       </c>
       <c r="D4" t="n">
-        <v>131.5964075203552</v>
+        <v>107.5642054680975</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.31208226342603</v>
+        <v>31.98043146583985</v>
       </c>
       <c r="C5" t="n">
-        <v>90.5416820241621</v>
+        <v>118.6932974434394</v>
       </c>
       <c r="D5" t="n">
-        <v>77.8280492541659</v>
+        <v>90.68894417979912</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.98748362621883</v>
+        <v>25.92206638293279</v>
       </c>
       <c r="C6" t="n">
-        <v>96.24170919501908</v>
+        <v>172.1160805177338</v>
       </c>
       <c r="D6" t="n">
-        <v>34.17365583712723</v>
+        <v>52.00513938936205</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.64280806657018</v>
+        <v>10.83947640258903</v>
       </c>
       <c r="C7" t="n">
-        <v>78.45145904636261</v>
+        <v>122.5280039762274</v>
       </c>
       <c r="D7" t="n">
-        <v>29.52409870981433</v>
+        <v>37.18958478457343</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.59796646734432</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>51.15396412978005</v>
+        <v>60.4167537193487</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>32.61562223048752</v>
+        <v>38.05155926890212</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>27.75891633757857</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>31.24313893995049</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.63872651149973</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.825289966373073</v>
+        <v>0.5301437602932776</v>
       </c>
       <c r="C2" t="n">
-        <v>2.655627539987622</v>
+        <v>2.366011967234813</v>
       </c>
       <c r="D2" t="n">
-        <v>26.70844629403447</v>
+        <v>7.795076771719675</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.42788743479814</v>
+        <v>3.445934441906305</v>
       </c>
       <c r="C3" t="n">
-        <v>27.58711048933537</v>
+        <v>9.842020735074275</v>
       </c>
       <c r="D3" t="n">
-        <v>115.1442794925872</v>
+        <v>53.71632563786423</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.76863600362979</v>
+        <v>14.3580601746096</v>
       </c>
       <c r="C4" t="n">
-        <v>91.08753374772331</v>
+        <v>32.65980087717864</v>
       </c>
       <c r="D4" t="n">
-        <v>154.1736594749191</v>
+        <v>112.2864119255247</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.85266539556753</v>
+        <v>32.61856747360028</v>
       </c>
       <c r="C5" t="n">
-        <v>127.136327699962</v>
+        <v>105.4397034361075</v>
       </c>
       <c r="D5" t="n">
-        <v>98.81290643244149</v>
+        <v>106.3969074477481</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.783722072092</v>
+        <v>32.00006641992479</v>
       </c>
       <c r="C6" t="n">
-        <v>119.2254046991412</v>
+        <v>189.6255508229757</v>
       </c>
       <c r="D6" t="n">
-        <v>43.71329827929349</v>
+        <v>64.00013283984957</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.50496247734813</v>
+        <v>12.99539436111503</v>
       </c>
       <c r="C7" t="n">
-        <v>103.0648557395344</v>
+        <v>174.0304885410151</v>
       </c>
       <c r="D7" t="n">
-        <v>32.33876937788993</v>
+        <v>41.02232782195297</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>68.51126354086365</v>
+        <v>92.21065312138165</v>
       </c>
       <c r="D8" t="n">
-        <v>28.28906009787184</v>
+        <v>41.55738032076748</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>37.60780930658255</v>
+        <v>50.25468323268996</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.030475236560656</v>
+        <v>0.9120436172452868</v>
       </c>
       <c r="C2" t="n">
-        <v>4.298091449192536</v>
+        <v>7.327764864498192</v>
       </c>
       <c r="D2" t="n">
-        <v>21.86548486898496</v>
+        <v>10.9896838013388</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.84036033930204</v>
+        <v>2.596722677732814</v>
       </c>
       <c r="C3" t="n">
-        <v>18.49612674800991</v>
+        <v>9.547496423800231</v>
       </c>
       <c r="D3" t="n">
-        <v>110.9767604880595</v>
+        <v>47.89456175168064</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.03887866420492</v>
+        <v>10.56753228851267</v>
       </c>
       <c r="C4" t="n">
-        <v>79.7031873692773</v>
+        <v>28.30771330425253</v>
       </c>
       <c r="D4" t="n">
-        <v>173.1773497860246</v>
+        <v>113.6009721015112</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.37561812676159</v>
+        <v>28.02889695624644</v>
       </c>
       <c r="C5" t="n">
-        <v>147.0658060961722</v>
+        <v>82.95768100885549</v>
       </c>
       <c r="D5" t="n">
-        <v>126.1545799957152</v>
+        <v>121.0249482410256</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.31078172055229</v>
+        <v>38.19882142453915</v>
       </c>
       <c r="C6" t="n">
-        <v>159.4770605732604</v>
+        <v>179.8041467896906</v>
       </c>
       <c r="D6" t="n">
-        <v>60.17622553180826</v>
+        <v>80.10079518949728</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.32636651063322</v>
+        <v>23.95464398362217</v>
       </c>
       <c r="C7" t="n">
-        <v>136.0623778269739</v>
+        <v>225.4131998858846</v>
       </c>
       <c r="D7" t="n">
-        <v>36.47094546506476</v>
+        <v>48.56804067679396</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.01797455831271</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>99.30378028456487</v>
+        <v>157.8012172421111</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>43.22635141798705</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>3.660937189136355</v>
       </c>
       <c r="C9" t="n">
-        <v>57.79843259212245</v>
+        <v>79.76405572694058</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>43.4874963073167</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>37.29659528433633</v>
+        <v>45.69544689416779</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.59224021203486</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>43.39815726623026</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.997275741065512</v>
+        <v>0.5900303702523331</v>
       </c>
       <c r="C2" t="n">
-        <v>2.02534551386117</v>
+        <v>3.575525138866883</v>
       </c>
       <c r="D2" t="n">
-        <v>15.30151971839079</v>
+        <v>7.824529202847079</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.57037972063417</v>
+        <v>3.907355862902306</v>
       </c>
       <c r="C3" t="n">
-        <v>18.76119862815655</v>
+        <v>18.6679325962531</v>
       </c>
       <c r="D3" t="n">
-        <v>108.3162242095506</v>
+        <v>51.57120690408495</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.65898336039042</v>
+        <v>18.37831702350029</v>
       </c>
       <c r="C4" t="n">
-        <v>75.83608316224911</v>
+        <v>41.69580674706629</v>
       </c>
       <c r="D4" t="n">
-        <v>186.8206976319426</v>
+        <v>119.7653659364769</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.40645321622075</v>
+        <v>24.3473430653209</v>
       </c>
       <c r="C5" t="n">
-        <v>169.8423528346982</v>
+        <v>137.5919407501905</v>
       </c>
       <c r="D5" t="n">
-        <v>133.4440566997477</v>
+        <v>114.2754327743287</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.17994723398021</v>
+        <v>14.85286101755</v>
       </c>
       <c r="C6" t="n">
-        <v>191.0343587785699</v>
+        <v>199.5677098238831</v>
       </c>
       <c r="D6" t="n">
-        <v>58.48565598509524</v>
+        <v>68.46806664187682</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>138.1584091755409</v>
+        <v>110.9698882541297</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>37.96811071404115</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>2.503456645829366</v>
       </c>
       <c r="C8" t="n">
-        <v>73.68507394224434</v>
+        <v>58.74778262212912</v>
       </c>
       <c r="D8" t="n">
-        <v>31.62700229231099</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>28.39999758845172</v>
+        <v>34.83437204208531</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>25.33890824661018</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>22.21204180858408</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>36.55046702910875</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.734568266954867</v>
+        <v>0.3681553890925539</v>
       </c>
       <c r="C2" t="n">
-        <v>6.609125544989528</v>
+        <v>1.863357142660446</v>
       </c>
       <c r="D2" t="n">
-        <v>16.59840843570083</v>
+        <v>6.083890523217484</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.64553232550467</v>
+        <v>2.925608158655495</v>
       </c>
       <c r="C3" t="n">
-        <v>13.233959053247</v>
+        <v>16.1448409963388</v>
       </c>
       <c r="D3" t="n">
-        <v>96.70705760683205</v>
+        <v>45.90652265058085</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.20479402622264</v>
+        <v>12.06077054667207</v>
       </c>
       <c r="C4" t="n">
-        <v>61.52907386826035</v>
+        <v>42.80616340056942</v>
       </c>
       <c r="D4" t="n">
-        <v>198.3964848127167</v>
+        <v>113.9455655457018</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.09554229361077</v>
+        <v>21.47573103039898</v>
       </c>
       <c r="C5" t="n">
-        <v>157.1041763720958</v>
+        <v>96.65306148309851</v>
       </c>
       <c r="D5" t="n">
-        <v>161.8901964302991</v>
+        <v>118.0306177430728</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.65796055495717</v>
+        <v>15.17487426454295</v>
       </c>
       <c r="C6" t="n">
-        <v>228.1061338386337</v>
+        <v>176.7852725991317</v>
       </c>
       <c r="D6" t="n">
-        <v>79.25551041614078</v>
+        <v>74.38506005537235</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.22360179685679</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>199.4822977736137</v>
+        <v>142.64990492247</v>
       </c>
       <c r="D7" t="n">
-        <v>42.57937968088841</v>
+        <v>37.36924461445059</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>118.1631536831461</v>
+        <v>66.00780689503429</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>27.45457454926205</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>51.69687061022852</v>
+        <v>32.17187226816797</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>22.18749811597791</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>20.35653864755762</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>14.39340309196248</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.94732978133594</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.616357631817749</v>
+        <v>0.4702571503342222</v>
       </c>
       <c r="C2" t="n">
-        <v>4.32754388031994</v>
+        <v>4.032037821341651</v>
       </c>
       <c r="D2" t="n">
-        <v>12.46917759163874</v>
+        <v>11.95179655150067</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.15327581504952</v>
+        <v>1.983130362578557</v>
       </c>
       <c r="C3" t="n">
-        <v>19.13426275577033</v>
+        <v>10.58324025178062</v>
       </c>
       <c r="D3" t="n">
-        <v>89.79555376893451</v>
+        <v>39.92277039319654</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.67853619901734</v>
+        <v>8.640361545076178</v>
       </c>
       <c r="C4" t="n">
-        <v>50.82115165804039</v>
+        <v>41.4150269036517</v>
       </c>
       <c r="D4" t="n">
-        <v>201.3957240491907</v>
+        <v>111.571699596833</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.05965959691014</v>
+        <v>20.39580855572749</v>
       </c>
       <c r="C5" t="n">
-        <v>145.7159030028328</v>
+        <v>87.30191460014763</v>
       </c>
       <c r="D5" t="n">
-        <v>185.378510254404</v>
+        <v>133.8367557814464</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.75483478250812</v>
+        <v>22.74218556887737</v>
       </c>
       <c r="C6" t="n">
-        <v>246.782902164225</v>
+        <v>166.4003453836089</v>
       </c>
       <c r="D6" t="n">
-        <v>95.91969594802613</v>
+        <v>95.07441117466963</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.96598298771663</v>
+        <v>11.61800233205675</v>
       </c>
       <c r="C7" t="n">
-        <v>247.3316991308989</v>
+        <v>207.6867633380042</v>
       </c>
       <c r="D7" t="n">
-        <v>48.92736033654828</v>
+        <v>49.88554609589318</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>3.254493639578176</v>
       </c>
       <c r="C8" t="n">
-        <v>155.0474149316988</v>
+        <v>132.9335478935394</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.8874999246391163</v>
       </c>
       <c r="C9" t="n">
-        <v>61.23749480009903</v>
+        <v>58.57499502618167</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>24.4062479275757</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.78359889890498</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>19.19120412261664</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>18.65811511921063</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.942698780255191</v>
+        <v>0.5900303702523331</v>
       </c>
       <c r="C2" t="n">
-        <v>10.42223362828414</v>
+        <v>6.314601233715485</v>
       </c>
       <c r="D2" t="n">
-        <v>15.44681837861931</v>
+        <v>13.18290817262617</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.13440162449058</v>
+        <v>1.776963344686727</v>
       </c>
       <c r="C3" t="n">
-        <v>17.89235190989812</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D3" t="n">
-        <v>80.75365741282138</v>
+        <v>40.21729470447059</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.08020987877453</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C4" t="n">
-        <v>49.28962523941536</v>
+        <v>32.81295351904114</v>
       </c>
       <c r="D4" t="n">
-        <v>199.8897230708761</v>
+        <v>106.6835777773881</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67.15154297048184</v>
+        <v>17.05786636128833</v>
       </c>
       <c r="C5" t="n">
-        <v>122.8657251864883</v>
+        <v>81.36234098945442</v>
       </c>
       <c r="D5" t="n">
-        <v>206.8787849774092</v>
+        <v>144.4887183725243</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>69.19259644761097</v>
+        <v>25.76105975943631</v>
       </c>
       <c r="C6" t="n">
-        <v>243.9652862530367</v>
+        <v>152.4732724511637</v>
       </c>
       <c r="D6" t="n">
-        <v>119.7084245696306</v>
+        <v>115.2404907676034</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.03366682604743</v>
+        <v>19.52303484665207</v>
       </c>
       <c r="C7" t="n">
-        <v>291.8274503304771</v>
+        <v>227.928437504165</v>
       </c>
       <c r="D7" t="n">
-        <v>60.36570283872788</v>
+        <v>64.13855926614836</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>221.8062588204818</v>
+        <v>209.539321255918</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>110.0499906552504</v>
+        <v>114.0437403161264</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>26.73593522975338</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>45.26838664282043</v>
+        <v>50.39310965898878</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>22.06477965294707</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>19.19120412261664</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>9.675123625352315</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.551783267515713</v>
+        <v>5.05992766768806</v>
       </c>
       <c r="C2" t="n">
-        <v>3.431208226342602</v>
+        <v>7.172648727227196</v>
       </c>
       <c r="D2" t="n">
-        <v>19.47198396603124</v>
+        <v>14.1126232485479</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.82252464970958</v>
+        <v>1.367574552015807</v>
       </c>
       <c r="C2" t="n">
-        <v>5.91895690890402</v>
+        <v>9.226464924511523</v>
       </c>
       <c r="D2" t="n">
-        <v>11.36962016288231</v>
+        <v>15.11793289769663</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.44427404613408</v>
+        <v>1.884955592153876</v>
       </c>
       <c r="C3" t="n">
-        <v>27.37603473292231</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D3" t="n">
-        <v>87.63080008107029</v>
+        <v>41.14995502350506</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.65523629602267</v>
+        <v>4.671155576806323</v>
       </c>
       <c r="C4" t="n">
-        <v>71.85411447382405</v>
+        <v>33.43832680664636</v>
       </c>
       <c r="D4" t="n">
-        <v>203.2463184716959</v>
+        <v>103.0717279734641</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.84070449666732</v>
+        <v>13.57266201121216</v>
       </c>
       <c r="C5" t="n">
-        <v>196.8158710088794</v>
+        <v>69.92498023497909</v>
       </c>
       <c r="D5" t="n">
-        <v>186.7038696551372</v>
+        <v>148.5875150377548</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.73589417202438</v>
+        <v>25.1170332654504</v>
       </c>
       <c r="C6" t="n">
-        <v>240.020623977373</v>
+        <v>141.7260803327738</v>
       </c>
       <c r="D6" t="n">
-        <v>93.22283500446015</v>
+        <v>133.5147425344535</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.988660995905543</v>
+        <v>24.97271635292611</v>
       </c>
       <c r="C7" t="n">
-        <v>155.9447323333803</v>
+        <v>227.3295714045744</v>
       </c>
       <c r="D7" t="n">
-        <v>34.55457394637499</v>
+        <v>79.64919124554372</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>14.18625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>81.11199532487147</v>
+        <v>258.1063801850077</v>
       </c>
       <c r="D8" t="n">
-        <v>24.95111790343269</v>
+        <v>44.97877107006762</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>184.9327967966759</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>29.7312474754104</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.9964739198105126</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>89.25559253159878</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>23.20360698987336</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.17036643664921</v>
+        <v>41.04785326226338</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>16.05550195525234</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>10.40652566501619</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.609305471438775</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.7166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.781512230309467</v>
+        <v>6.294966279630549</v>
       </c>
       <c r="C2" t="n">
-        <v>4.420809912223387</v>
+        <v>4.757549374780043</v>
       </c>
       <c r="D2" t="n">
-        <v>19.45038551653781</v>
+        <v>12.29835349109979</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.79569866652543</v>
+        <v>8.354672963140358</v>
       </c>
       <c r="C3" t="n">
-        <v>8.644288535893166</v>
+        <v>14.16171063376024</v>
       </c>
       <c r="D3" t="n">
-        <v>19.49260066782042</v>
+        <v>12.63018421513522</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39711800594602</v>
+        <v>11.67771969972413</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1378530899527</v>
+        <v>59.94562779191722</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576131530111296</v>
+        <v>0.7785146466482755</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.055599766243573</v>
+        <v>2.87161203492192</v>
       </c>
       <c r="C2" t="n">
-        <v>6.977280934082081</v>
+        <v>3.218168974521045</v>
       </c>
       <c r="D2" t="n">
-        <v>20.85232123820225</v>
+        <v>19.90297120819559</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.71425466480195</v>
+        <v>16.87133429748144</v>
       </c>
       <c r="C3" t="n">
-        <v>14.01935721664445</v>
+        <v>17.12658870058561</v>
       </c>
       <c r="D3" t="n">
-        <v>31.12140222462389</v>
+        <v>20.27799883121787</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.7582123273148</v>
+        <v>10.36332876602933</v>
       </c>
       <c r="C4" t="n">
-        <v>13.73268688700438</v>
+        <v>23.57274412667016</v>
       </c>
       <c r="D4" t="n">
-        <v>25.28294862746811</v>
+        <v>20.930861054542</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.448699758569798</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>35.01894061048373</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>21.07812321017901</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44001395203293</v>
+        <v>13.629804823607</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13902520607847</v>
+        <v>73.76129669246141</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250529253059565</v>
+        <v>1.603506449836118</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.028912651779663</v>
+        <v>2.16377194015997</v>
       </c>
       <c r="C2" t="n">
-        <v>5.972953032637593</v>
+        <v>5.052073686054086</v>
       </c>
       <c r="D2" t="n">
-        <v>30.90934472050658</v>
+        <v>23.04358211408113</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.20727193878309</v>
+        <v>12.87071240267569</v>
       </c>
       <c r="C3" t="n">
-        <v>21.98133109808609</v>
+        <v>14.19116306488765</v>
       </c>
       <c r="D3" t="n">
-        <v>40.58054135504191</v>
+        <v>32.09333245182823</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.23640557474101</v>
+        <v>23.84076124992954</v>
       </c>
       <c r="C4" t="n">
-        <v>26.30396623988479</v>
+        <v>35.7483791547391</v>
       </c>
       <c r="D4" t="n">
-        <v>35.18681946790993</v>
+        <v>26.49540704221292</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.34547738090364</v>
+        <v>9.621127501618743</v>
       </c>
       <c r="C5" t="n">
-        <v>16.73879835740812</v>
+        <v>28.51977080836985</v>
       </c>
       <c r="D5" t="n">
-        <v>31.48955761371645</v>
+        <v>27.68528525976006</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.8302651248191</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.18437294641592</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73520749277658</v>
+        <v>14.84285243688858</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0847657059372</v>
+        <v>87.40790879501051</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020562247832975</v>
+        <v>2.473808739481429</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.944883259841937</v>
+        <v>2.440624792757571</v>
       </c>
       <c r="C2" t="n">
-        <v>6.998879383575511</v>
+        <v>5.402557616470197</v>
       </c>
       <c r="D2" t="n">
-        <v>27.57827475999715</v>
+        <v>21.27250925561989</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.19669369821463</v>
+        <v>9.807659565425636</v>
       </c>
       <c r="C3" t="n">
-        <v>22.66364575253762</v>
+        <v>17.57328390601791</v>
       </c>
       <c r="D3" t="n">
-        <v>55.04168503859743</v>
+        <v>43.07908926235004</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.18459393059418</v>
+        <v>24.81072798172539</v>
       </c>
       <c r="C4" t="n">
-        <v>42.07868835172254</v>
+        <v>35.65904011365264</v>
       </c>
       <c r="D4" t="n">
-        <v>46.94128473085699</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.24916829489622</v>
+        <v>23.4392264388926</v>
       </c>
       <c r="C5" t="n">
-        <v>34.23845118560752</v>
+        <v>50.31456984264904</v>
       </c>
       <c r="D5" t="n">
-        <v>36.47192721276901</v>
+        <v>31.29320807286709</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.39121861237574</v>
+        <v>9.096874227550947</v>
       </c>
       <c r="C6" t="n">
-        <v>19.80381469006666</v>
+        <v>29.82647700272235</v>
       </c>
       <c r="D6" t="n">
-        <v>38.84284791852506</v>
+        <v>34.09315252537899</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>39.40538935305847</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.79389940203295</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.50740899884213</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06290434007563</v>
+        <v>16.09061913519028</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8389473614458</v>
+        <v>101.6249629590965</v>
       </c>
       <c r="D21" t="n">
-        <v>6.881106415266908</v>
+        <v>3.387498765303218</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.082327938436491</v>
+        <v>2.474985962406209</v>
       </c>
       <c r="C2" t="n">
-        <v>7.159886007071988</v>
+        <v>5.725552611167398</v>
       </c>
       <c r="D2" t="n">
-        <v>31.92839883751477</v>
+        <v>19.24912723716721</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.00663555421825</v>
+        <v>9.027170140549421</v>
       </c>
       <c r="C3" t="n">
-        <v>23.72393327312417</v>
+        <v>19.57114048416017</v>
       </c>
       <c r="D3" t="n">
-        <v>59.98478472948011</v>
+        <v>49.66170761932491</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.93460811890974</v>
+        <v>21.8370141855618</v>
       </c>
       <c r="C4" t="n">
-        <v>41.75962034784233</v>
+        <v>40.39400929123502</v>
       </c>
       <c r="D4" t="n">
-        <v>54.63720498444773</v>
+        <v>48.70254011227577</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.9785657814226</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="C5" t="n">
-        <v>43.12326790904115</v>
+        <v>58.41398840268523</v>
       </c>
       <c r="D5" t="n">
-        <v>36.61918936840603</v>
+        <v>37.38004383919731</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.23650338573225</v>
+        <v>20.76985443104552</v>
       </c>
       <c r="C6" t="n">
-        <v>25.51954982419159</v>
+        <v>56.79508643838223</v>
       </c>
       <c r="D6" t="n">
-        <v>32.28182801104362</v>
+        <v>36.22649028670731</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.569454726192155</v>
+        <v>8.863218273940204</v>
       </c>
       <c r="C7" t="n">
-        <v>16.16938468894497</v>
+        <v>31.20092378866788</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>38.2734342500619</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.060914526761252</v>
+        <v>17.36864468126204</v>
       </c>
       <c r="C21" t="n">
-        <v>66.19607368838673</v>
+        <v>115.5014871303926</v>
       </c>
       <c r="D21" t="n">
-        <v>5.295685895070939</v>
+        <v>4.34216117031551</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.458918146239766</v>
+        <v>3.12097595180061</v>
       </c>
       <c r="C2" t="n">
-        <v>8.883834975729387</v>
+        <v>6.320491719940965</v>
       </c>
       <c r="D2" t="n">
-        <v>31.96963224109313</v>
+        <v>28.24193620806799</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.62437584436775</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C3" t="n">
-        <v>26.52682296874882</v>
+        <v>21.00940087088174</v>
       </c>
       <c r="D3" t="n">
-        <v>73.58689917181968</v>
+        <v>52.95056242855171</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.88127494771092</v>
+        <v>19.41209735607218</v>
       </c>
       <c r="C4" t="n">
-        <v>53.13120400613313</v>
+        <v>44.59294422229862</v>
       </c>
       <c r="D4" t="n">
-        <v>72.87513208624073</v>
+        <v>60.64844617755096</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.37250865273283</v>
+        <v>32.12769362147687</v>
       </c>
       <c r="C5" t="n">
-        <v>64.35356201337844</v>
+        <v>66.97973712223865</v>
       </c>
       <c r="D5" t="n">
-        <v>49.2837347531899</v>
+        <v>45.94579255875073</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.01136436629024</v>
+        <v>30.79251674370121</v>
       </c>
       <c r="C6" t="n">
-        <v>51.20010627187966</v>
+        <v>75.27059648460298</v>
       </c>
       <c r="D6" t="n">
-        <v>36.8302651248191</v>
+        <v>39.44662275663685</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.83947640258903</v>
+        <v>16.64847756861741</v>
       </c>
       <c r="C7" t="n">
-        <v>28.50602634051038</v>
+        <v>56.77250624118454</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>39.58504918293564</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
-        <v>20.69524160552276</v>
+        <v>33.29597338953057</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>39.22082078466007</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.542186774651494</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>39.160934174701</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.7341359652609</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.65056423721292</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.284179911745652</v>
+        <v>18.67179596365023</v>
       </c>
       <c r="C21" t="n">
-        <v>75.57336658436115</v>
+        <v>128.9243054632992</v>
       </c>
       <c r="D21" t="n">
-        <v>6.373657422777446</v>
+        <v>5.334798846757208</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.975898275750335</v>
+        <v>2.747911824186823</v>
       </c>
       <c r="C2" t="n">
-        <v>4.015348110369454</v>
+        <v>3.791509633801182</v>
       </c>
       <c r="D2" t="n">
-        <v>26.37170683147782</v>
+        <v>22.01667401543897</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.48693116577319</v>
+        <v>12.4976482750619</v>
       </c>
       <c r="C3" t="n">
-        <v>31.40610905885546</v>
+        <v>31.92152660358504</v>
       </c>
       <c r="D3" t="n">
-        <v>82.08883429059705</v>
+        <v>59.97987599095887</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.67104207028186</v>
+        <v>15.43012866764712</v>
       </c>
       <c r="C4" t="n">
-        <v>60.99303962174159</v>
+        <v>62.11615899539994</v>
       </c>
       <c r="D4" t="n">
-        <v>93.39758609581605</v>
+        <v>57.73854598216341</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.22082078466008</v>
+        <v>17.32784697995621</v>
       </c>
       <c r="C5" t="n">
-        <v>83.08039947188634</v>
+        <v>44.96404485450392</v>
       </c>
       <c r="D5" t="n">
-        <v>63.86268816125503</v>
+        <v>37.23278168356029</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.43025184083414</v>
+        <v>10.30442390377452</v>
       </c>
       <c r="C6" t="n">
-        <v>79.81903359837844</v>
+        <v>37.39378830705677</v>
       </c>
       <c r="D6" t="n">
-        <v>44.31707311740527</v>
+        <v>26.04282135055514</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.68462230722529</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>53.71828913327272</v>
+        <v>23.41566449399068</v>
       </c>
       <c r="D7" t="n">
-        <v>36.83026512481909</v>
+        <v>27.5478405811655</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>30.37527396939631</v>
+        <v>23.53249247079604</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>25.4046853427947</v>
+        <v>26.5140602485936</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -6504,7 +6504,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
         <v>26.65445017030089</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.494432634130789</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.24917121323772</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.494432634130789</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
